--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009571B3-EC72-4378-9B2B-25D706B2584E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB1732C-9118-4793-850E-69C926777FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
     <t>Group</t>
   </si>
   <si>
-    <t>UnitId[]</t>
+    <t>UnitId</t>
   </si>
 </sst>
 </file>
@@ -509,67 +509,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1647,7 +1587,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A11:A16">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB1732C-9118-4793-850E-69C926777FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3822574-6427-420E-9232-D64D8BD50B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5200" yWindow="5200" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -802,7 +802,7 @@
     <col min="1" max="1" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="39.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.90625" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.7265625" style="1"/>
     <col min="6" max="6" width="27.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.7265625" style="1"/>
@@ -1587,7 +1587,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A11:A16">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3822574-6427-420E-9232-D64D8BD50B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ED5F66-A68C-478A-A8BD-F78D1D0F501E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5200" yWindow="5200" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="198">
   <si>
     <t>id</t>
   </si>
@@ -448,6 +448,189 @@
   </si>
   <si>
     <t>UnitId</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>Enum:SkillTag[]</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>thunder</t>
+  </si>
+  <si>
+    <t>battle</t>
+  </si>
+  <si>
+    <t>holy</t>
+  </si>
+  <si>
+    <t>xskill</t>
+  </si>
+  <si>
+    <t>thunder,summon</t>
+  </si>
+  <si>
+    <t>thunder,guardian</t>
+  </si>
+  <si>
+    <t>battle,fire</t>
+  </si>
+  <si>
+    <t>xskill,thunder</t>
+  </si>
+  <si>
+    <t>holy,guardian</t>
+  </si>
+  <si>
+    <t>posx</t>
+  </si>
+  <si>
+    <t>prerequisite</t>
+  </si>
+  <si>
+    <t>SkillId[]</t>
+  </si>
+  <si>
+    <t>坐标x</t>
+  </si>
+  <si>
+    <t>前置技能</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>图标</t>
+  </si>
+  <si>
+    <t>Spell_Fire_FireBolt</t>
+  </si>
+  <si>
+    <t>Spell_Fire_SealOfFire</t>
+  </si>
+  <si>
+    <t>Spell_Fire_Incinerate</t>
+  </si>
+  <si>
+    <t>Spell_Fire_Fireball02</t>
+  </si>
+  <si>
+    <t>Spell_Fire_Volcano</t>
+  </si>
+  <si>
+    <t>Spell_Fire_SelfDestruct</t>
+  </si>
+  <si>
+    <t>Spell_Shadow_Charm</t>
+  </si>
+  <si>
+    <t>Spell_Nature_Lightning</t>
+  </si>
+  <si>
+    <t>Spell_Nature_LightningBolt</t>
+  </si>
+  <si>
+    <t>Spell_Nature_LightningOverload</t>
+  </si>
+  <si>
+    <t>Spell_Nature_LightningShield</t>
+  </si>
+  <si>
+    <t>Spell_Frost_IceStorm</t>
+  </si>
+  <si>
+    <t>Ability_MeleeDamage</t>
+  </si>
+  <si>
+    <t>Ability_CriticalStrike</t>
+  </si>
+  <si>
+    <t>Ability_BackStab</t>
+  </si>
+  <si>
+    <t>Ability_Warrior_Cleave</t>
+  </si>
+  <si>
+    <t>Ability_Warrior_Challange</t>
+  </si>
+  <si>
+    <t>Ability_Warrior_PunishingBlow</t>
+  </si>
+  <si>
+    <t>Ability_Warrior_ImprovedDisciplines</t>
+  </si>
+  <si>
+    <t>Ability_Stealth</t>
+  </si>
+  <si>
+    <t>Ability_Warrior_RallyingCry</t>
+  </si>
+  <si>
+    <t>Ability_Warlock_EmpoweredImp</t>
+  </si>
+  <si>
+    <t>Ability_Warrior_SecondWind</t>
+  </si>
+  <si>
+    <t>Spell_Frost_FreezingBreath</t>
+  </si>
+  <si>
+    <t>Spell_Holy_Heal</t>
+  </si>
+  <si>
+    <t>Spell_Holy_GreaterBlessingofSanctuary</t>
+  </si>
+  <si>
+    <t>Spell_Magic_LesserInvisibilty</t>
+  </si>
+  <si>
+    <t>Spell_Holy_BlessingOfProtection</t>
+  </si>
+  <si>
+    <t>Spell_Holy_HolySmite</t>
+  </si>
+  <si>
+    <t>Spell_Nature_Slow</t>
+  </si>
+  <si>
+    <t>Spell_Holy_RighteousnessAura</t>
+  </si>
+  <si>
+    <t>Spell_Shadow_AbominationExplosion</t>
+  </si>
+  <si>
+    <t>Spell_Shadow_RaiseDead</t>
+  </si>
+  <si>
+    <t>Spell_Fire_Rune</t>
+  </si>
+  <si>
+    <t>Spell_Holy_WeaponMastery</t>
+  </si>
+  <si>
+    <t>Spell_Fire_Elemental_Totem</t>
+  </si>
+  <si>
+    <t>hhel,hlok</t>
+  </si>
+  <si>
+    <t>psyco,battle</t>
+  </si>
+  <si>
+    <t>psyco,summon</t>
+  </si>
+  <si>
+    <t>psyco,fire</t>
+  </si>
+  <si>
+    <t>psyco,poison</t>
   </si>
 </sst>
 </file>
@@ -509,7 +692,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -796,19 +1019,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="50.90625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" style="1"/>
-    <col min="6" max="6" width="27.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="1"/>
+    <col min="3" max="3" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="50.90625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="1"/>
+    <col min="10" max="10" width="27.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,31 +1042,43 @@
         <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -848,31 +1086,43 @@
         <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>116</v>
+        <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>116</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>116</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -880,7 +1130,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -888,31 +1138,43 @@
         <v>131</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
@@ -920,25 +1182,34 @@
         <v>132</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="1">
+      <c r="K5" s="1">
         <v>7</v>
       </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -946,25 +1217,37 @@
         <v>132</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="1">
+      <c r="I6" s="1">
         <v>7</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="1">
+      <c r="K6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="1">
+      <c r="L6" s="1">
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -972,31 +1255,43 @@
         <v>132</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="1">
+      <c r="I7" s="1">
         <v>14</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G7" s="1">
+      <c r="K7" s="1">
         <v>29</v>
       </c>
-      <c r="H7" s="1">
+      <c r="L7" s="1">
         <v>1.2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="M7" s="1">
         <v>2</v>
       </c>
-      <c r="J7" s="1">
+      <c r="N7" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
@@ -1004,25 +1299,37 @@
         <v>132</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="1">
+      <c r="I8" s="1">
         <v>21</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G8" s="1">
+      <c r="K8" s="1">
         <v>63</v>
       </c>
-      <c r="H8" s="1">
+      <c r="L8" s="1">
         <v>1.25</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1030,25 +1337,37 @@
         <v>132</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="1">
+      <c r="I9" s="1">
         <v>28</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G9" s="1">
+      <c r="K9" s="1">
         <v>25</v>
       </c>
-      <c r="H9" s="1">
+      <c r="L9" s="1">
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
@@ -1056,25 +1375,37 @@
         <v>132</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="1">
+      <c r="I10" s="1">
         <v>35</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G10" s="1">
+      <c r="K10" s="1">
         <v>57</v>
       </c>
-      <c r="H10" s="1">
+      <c r="L10" s="1">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -1082,16 +1413,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
@@ -1099,16 +1439,25 @@
         <v>132</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="1">
+      <c r="I12" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
@@ -1116,16 +1465,28 @@
         <v>132</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="1">
+      <c r="I13" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1133,16 +1494,28 @@
         <v>132</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="1">
+      <c r="I14" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
@@ -1150,16 +1523,28 @@
         <v>132</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="1">
+      <c r="I15" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
@@ -1167,16 +1552,28 @@
         <v>132</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="1">
+      <c r="I16" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1184,16 +1581,25 @@
         <v>133</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>57</v>
       </c>
@@ -1201,16 +1607,28 @@
         <v>133</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="1">
+      <c r="I18" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
@@ -1218,16 +1636,28 @@
         <v>133</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="1">
+      <c r="I19" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>59</v>
       </c>
@@ -1235,16 +1665,28 @@
         <v>133</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="1">
+      <c r="I20" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>60</v>
       </c>
@@ -1252,16 +1694,28 @@
         <v>133</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="1">
+      <c r="I21" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>61</v>
       </c>
@@ -1269,16 +1723,28 @@
         <v>133</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E22" s="1">
+      <c r="I22" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>62</v>
       </c>
@@ -1286,16 +1752,25 @@
         <v>133</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
@@ -1303,16 +1778,25 @@
         <v>133</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="1">
+      <c r="I24" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
@@ -1320,16 +1804,25 @@
         <v>133</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="1">
+      <c r="I25" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -1337,16 +1830,25 @@
         <v>133</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="1">
+      <c r="I26" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
@@ -1354,16 +1856,28 @@
         <v>133</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="1">
+      <c r="I27" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>67</v>
       </c>
@@ -1371,16 +1885,28 @@
         <v>133</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="1">
+      <c r="I28" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>68</v>
       </c>
@@ -1388,16 +1914,25 @@
         <v>134</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>69</v>
       </c>
@@ -1405,16 +1940,25 @@
         <v>134</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="1">
+      <c r="I30" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>70</v>
       </c>
@@ -1422,16 +1966,25 @@
         <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="1">
+      <c r="I31" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>71</v>
       </c>
@@ -1439,16 +1992,28 @@
         <v>134</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="1">
+      <c r="I32" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>72</v>
       </c>
@@ -1456,16 +2021,28 @@
         <v>134</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="1">
+      <c r="I33" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>73</v>
       </c>
@@ -1473,16 +2050,28 @@
         <v>134</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="1">
+      <c r="I34" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>74</v>
       </c>
@@ -1490,16 +2079,25 @@
         <v>134</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>75</v>
       </c>
@@ -1507,16 +2105,25 @@
         <v>134</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E36" s="1">
+      <c r="I36" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>79</v>
       </c>
@@ -1524,16 +2131,25 @@
         <v>134</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E37" s="1">
+      <c r="I37" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
@@ -1541,16 +2157,28 @@
         <v>134</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E38" s="1">
+      <c r="I38" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1558,16 +2186,28 @@
         <v>134</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E39" s="1">
+      <c r="I39" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -1575,19 +2215,43 @@
         <v>134</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E40" s="1">
+      <c r="I40" s="1">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A11:A16">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ED5F66-A68C-478A-A8BD-F78D1D0F501E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A8FC2D-3607-4C97-AA4C-4BA3B2E0E596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2200" yWindow="2550" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -692,7 +692,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1416,7 +1426,7 @@
         <v>145</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>163</v>
@@ -1529,7 +1539,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>167</v>
@@ -2239,16 +2249,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A11:A16">
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A8FC2D-3607-4C97-AA4C-4BA3B2E0E596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD27C2F7-D743-4562-8E20-2E29D7C05512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="2550" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="206">
   <si>
     <t>id</t>
   </si>
@@ -285,9 +285,6 @@
     <t>对第一列所有目标造成{0}点火焰伤害，并使其在当前回合无法攻击。</t>
   </si>
   <si>
-    <t>对任意一个目标造成{0}点火焰伤害并造成{1}回合的点燃效果，并且每回合会引燃临近的1个目标。</t>
-  </si>
-  <si>
     <t>对指定行的第一个目标造成{0}点火焰伤害，并对{1}个临近目标造成全额伤害。</t>
   </si>
   <si>
@@ -300,9 +297,6 @@
     <t>对任意一个目标造成{0}点风雷伤害。</t>
   </si>
   <si>
-    <t>对指定行所有目标造成{0}点风雷伤害。</t>
-  </si>
-  <si>
     <t>对指定2行或者2列的所有目标造成{0}点风雷伤害。</t>
   </si>
   <si>
@@ -363,9 +357,6 @@
     <t>对任意不死或者妖魔类敌人施展，使其在{0}回合内无法行动，同时降低其所有抗性{1}%，无法对精英和Boss施放。</t>
   </si>
   <si>
-    <t>有一定概率使目标敌人加入你的队伍，最多诱惑{0}个敌人，无法对精英和Boss施放。</t>
-  </si>
-  <si>
     <t>神圣责罚</t>
   </si>
   <si>
@@ -393,42 +384,18 @@
     <t>需求等级</t>
   </si>
   <si>
-    <t>num1</t>
-  </si>
-  <si>
     <t>参数1</t>
   </si>
   <si>
-    <t>num2</t>
-  </si>
-  <si>
     <t>参数2</t>
   </si>
   <si>
-    <t>公式</t>
-  </si>
-  <si>
-    <t>formula</t>
-  </si>
-  <si>
-    <t>$0=n1+fdmg*n2</t>
-  </si>
-  <si>
     <t>参数3</t>
   </si>
   <si>
     <t>参数4</t>
   </si>
   <si>
-    <t>num3</t>
-  </si>
-  <si>
-    <t>num4</t>
-  </si>
-  <si>
-    <t>$0=n1+fdmg*n2,$1=n3+fdmg*n4</t>
-  </si>
-  <si>
     <t>klass</t>
   </si>
   <si>
@@ -631,13 +598,70 @@
   </si>
   <si>
     <t>psyco,poison</t>
+  </si>
+  <si>
+    <t>n1</t>
+  </si>
+  <si>
+    <t>n2</t>
+  </si>
+  <si>
+    <t>n3</t>
+  </si>
+  <si>
+    <t>n4</t>
+  </si>
+  <si>
+    <t>n5</t>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>n6</t>
+  </si>
+  <si>
+    <t>n7</t>
+  </si>
+  <si>
+    <t>n8</t>
+  </si>
+  <si>
+    <t>n9</t>
+  </si>
+  <si>
+    <t>n10</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>参数7</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>参数9</t>
+  </si>
+  <si>
+    <t>参数10</t>
+  </si>
+  <si>
+    <t>有{0.2}%的概率使目标敌人加入你的队伍，最多诱惑{1}个敌人，无法对精英和Boss施放。每{2}点运气可提升1%成功率。</t>
+  </si>
+  <si>
+    <t>对指定行所有目标造成{0}点风雷伤害，法术命中-20%。</t>
+  </si>
+  <si>
+    <t>对任意一个目标造成{0}点火焰伤害并造成{1}回合的点燃效果，并且每回合会引燃临近的{2}个目标。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,6 +680,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -684,25 +714,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1029,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -1039,29 +1061,28 @@
     <col min="5" max="6" width="14.7265625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.6328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="50.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="1"/>
-    <col min="10" max="10" width="27.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="1"/>
+    <col min="9" max="9" width="8.7265625" style="3"/>
+    <col min="10" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1069,40 +1090,55 @@
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>115</v>
+      <c r="I1" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
@@ -1113,51 +1149,66 @@
       <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>116</v>
+      <c r="I2" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>6</v>
@@ -1165,40 +1216,55 @@
       <c r="H4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>9</v>
@@ -1206,28 +1272,34 @@
       <c r="H5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>124</v>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>3</v>
       </c>
       <c r="K5" s="1">
         <v>7</v>
       </c>
       <c r="L5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="M5" s="1">
+        <v>4</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1236,7 +1308,7 @@
         <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
@@ -1244,28 +1316,34 @@
       <c r="H6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="3">
         <v>7</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>124</v>
+      <c r="J6" s="1">
+        <v>1</v>
       </c>
       <c r="K6" s="1">
         <v>2</v>
       </c>
       <c r="L6" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="N6" s="1">
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
@@ -1274,42 +1352,51 @@
         <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="1">
+        <v>205</v>
+      </c>
+      <c r="I7" s="3">
         <v>14</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>129</v>
+      <c r="J7" s="1">
+        <v>12</v>
       </c>
       <c r="K7" s="1">
         <v>29</v>
       </c>
       <c r="L7" s="1">
+        <v>8</v>
+      </c>
+      <c r="M7" s="1">
+        <v>17</v>
+      </c>
+      <c r="N7" s="1">
         <v>1.2</v>
       </c>
-      <c r="M7" s="1">
+      <c r="O7" s="1">
         <v>2</v>
       </c>
-      <c r="N7" s="1">
+      <c r="P7" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1318,36 +1405,45 @@
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="1">
+        <v>82</v>
+      </c>
+      <c r="I8" s="3">
         <v>21</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>124</v>
+      <c r="J8" s="1">
+        <v>27</v>
       </c>
       <c r="K8" s="1">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="L8" s="1">
+        <v>18</v>
+      </c>
+      <c r="M8" s="1">
+        <v>36</v>
+      </c>
+      <c r="N8" s="1">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1356,36 +1452,42 @@
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I9" s="1">
+        <v>83</v>
+      </c>
+      <c r="I9" s="3">
         <v>28</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>124</v>
+      <c r="J9" s="1">
+        <v>11</v>
       </c>
       <c r="K9" s="1">
         <v>25</v>
       </c>
       <c r="L9" s="1">
+        <v>5</v>
+      </c>
+      <c r="M9" s="1">
+        <v>13</v>
+      </c>
+      <c r="N9" s="1">
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -1394,88 +1496,130 @@
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="1">
+        <v>84</v>
+      </c>
+      <c r="I10" s="3">
         <v>35</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>124</v>
+      <c r="J10" s="1">
+        <v>24</v>
       </c>
       <c r="K10" s="1">
         <v>57</v>
       </c>
       <c r="L10" s="1">
+        <v>12</v>
+      </c>
+      <c r="M10" s="1">
+        <v>32</v>
+      </c>
+      <c r="N10" s="1">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>25</v>
+      </c>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>75</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="O11" s="1">
+        <v>8</v>
+      </c>
+      <c r="P11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="1">
+        <v>85</v>
+      </c>
+      <c r="I12" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>22</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>12</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -1484,27 +1628,42 @@
         <v>51</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" s="1">
+        <v>204</v>
+      </c>
+      <c r="I13" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>35</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>19</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -1513,27 +1672,42 @@
         <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="1">
+        <v>86</v>
+      </c>
+      <c r="I14" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>105</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>37</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -1542,27 +1716,39 @@
         <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" s="1">
+        <v>87</v>
+      </c>
+      <c r="I15" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="J15" s="1">
+        <v>25</v>
+      </c>
+      <c r="K15" s="1">
+        <v>5</v>
+      </c>
+      <c r="L15" s="1">
+        <v>2</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -1571,16 +1757,31 @@
         <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I16" s="1">
+        <v>88</v>
+      </c>
+      <c r="I16" s="3">
         <v>35</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>72</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
+        <v>45</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1588,24 +1789,24 @@
         <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I17" s="1">
+        <v>89</v>
+      </c>
+      <c r="I17" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1614,10 +1815,10 @@
         <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1626,15 +1827,15 @@
         <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="1">
+        <v>90</v>
+      </c>
+      <c r="I18" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1643,10 +1844,10 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -1655,15 +1856,15 @@
         <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I19" s="1">
+        <v>91</v>
+      </c>
+      <c r="I19" s="3">
         <v>14</v>
       </c>
     </row>
@@ -1672,10 +1873,10 @@
         <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -1684,15 +1885,15 @@
         <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" s="1">
+        <v>92</v>
+      </c>
+      <c r="I20" s="3">
         <v>21</v>
       </c>
     </row>
@@ -1701,10 +1902,10 @@
         <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -1713,15 +1914,15 @@
         <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I21" s="1">
+        <v>93</v>
+      </c>
+      <c r="I21" s="3">
         <v>28</v>
       </c>
     </row>
@@ -1730,10 +1931,10 @@
         <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -1742,15 +1943,15 @@
         <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="1">
+        <v>94</v>
+      </c>
+      <c r="I22" s="3">
         <v>35</v>
       </c>
     </row>
@@ -1759,24 +1960,24 @@
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I23" s="1">
+        <v>95</v>
+      </c>
+      <c r="I23" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1785,24 +1986,24 @@
         <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I24" s="1">
+        <v>96</v>
+      </c>
+      <c r="I24" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1811,24 +2012,24 @@
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="1">
+        <v>97</v>
+      </c>
+      <c r="I25" s="3">
         <v>14</v>
       </c>
     </row>
@@ -1837,24 +2038,24 @@
         <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="1">
+        <v>98</v>
+      </c>
+      <c r="I26" s="3">
         <v>21</v>
       </c>
     </row>
@@ -1863,10 +2064,10 @@
         <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -1875,15 +2076,15 @@
         <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I27" s="1">
+        <v>99</v>
+      </c>
+      <c r="I27" s="3">
         <v>28</v>
       </c>
     </row>
@@ -1892,10 +2093,10 @@
         <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -1904,15 +2105,15 @@
         <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I28" s="1">
+        <v>100</v>
+      </c>
+      <c r="I28" s="3">
         <v>35</v>
       </c>
     </row>
@@ -1921,24 +2122,24 @@
         <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I29" s="1">
+        <v>101</v>
+      </c>
+      <c r="I29" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1947,24 +2148,24 @@
         <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I30" s="1">
+        <v>102</v>
+      </c>
+      <c r="I30" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1973,24 +2174,24 @@
         <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I31" s="1">
+        <v>103</v>
+      </c>
+      <c r="I31" s="3">
         <v>14</v>
       </c>
     </row>
@@ -1999,10 +2200,10 @@
         <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2011,15 +2212,15 @@
         <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I32" s="1">
+        <v>104</v>
+      </c>
+      <c r="I32" s="3">
         <v>21</v>
       </c>
     </row>
@@ -2028,10 +2229,10 @@
         <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -2040,15 +2241,15 @@
         <v>70</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I33" s="1">
+        <v>105</v>
+      </c>
+      <c r="I33" s="3">
         <v>28</v>
       </c>
     </row>
@@ -2057,27 +2258,27 @@
         <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I34" s="1">
+        <v>107</v>
+      </c>
+      <c r="I34" s="3">
         <v>35</v>
       </c>
     </row>
@@ -2086,24 +2287,24 @@
         <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I35" s="1">
+        <v>89</v>
+      </c>
+      <c r="I35" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2112,24 +2313,24 @@
         <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I36" s="1">
+        <v>108</v>
+      </c>
+      <c r="I36" s="3">
         <v>7</v>
       </c>
     </row>
@@ -2138,24 +2339,24 @@
         <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I37" s="1">
+        <v>109</v>
+      </c>
+      <c r="I37" s="3">
         <v>14</v>
       </c>
     </row>
@@ -2164,10 +2365,10 @@
         <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
@@ -2176,7 +2377,7 @@
         <v>75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>41</v>
@@ -2184,7 +2385,7 @@
       <c r="H38" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="3">
         <v>21</v>
       </c>
     </row>
@@ -2193,10 +2394,10 @@
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -2205,15 +2406,15 @@
         <v>74</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I39" s="1">
+        <v>110</v>
+      </c>
+      <c r="I39" s="3">
         <v>28</v>
       </c>
     </row>
@@ -2222,10 +2423,10 @@
         <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -2234,34 +2435,34 @@
         <v>79</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I40" s="1">
+        <v>111</v>
+      </c>
+      <c r="I40" s="3">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A11:A16">
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD27C2F7-D743-4562-8E20-2E29D7C05512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A579C577-1B02-4BCC-BD9A-99EB45AF93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="207">
   <si>
     <t>id</t>
   </si>
@@ -309,12 +309,6 @@
     <t>增加{0}%命中。</t>
   </si>
   <si>
-    <t>增加{0}%暴击几率。</t>
-  </si>
-  <si>
-    <t>对指定行的前2个目标造成{0}点物理伤害，并对第二目标增伤{1}%。</t>
-  </si>
-  <si>
     <t>对最靠前的一列所有目标造成{0}点物理伤害。</t>
   </si>
   <si>
@@ -655,17 +649,151 @@
   </si>
   <si>
     <t>对任意一个目标造成{0}点火焰伤害并造成{1}回合的点燃效果，并且每回合会引燃临近的{2}个目标。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0.2}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>命中。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0.2}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对指定行的前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个目标造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点物理伤害，并对第二目标增伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>{1.2}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -677,7 +805,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -686,6 +814,20 @@
       <color rgb="FF7030A0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -714,15 +856,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -1052,37 +1195,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="50.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="3"/>
-    <col min="10" max="16384" width="8.7265625" style="1"/>
+    <col min="5" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="50.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" style="3"/>
+    <col min="10" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1091,54 +1234,54 @@
         <v>2</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
@@ -1150,65 +1293,65 @@
         <v>3</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>6</v>
@@ -1217,54 +1360,54 @@
         <v>7</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="R4" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>9</v>
@@ -1291,15 +1434,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1308,7 +1451,7 @@
         <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
@@ -1335,15 +1478,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
@@ -1352,13 +1495,13 @@
         <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I7" s="3">
         <v>14</v>
@@ -1388,15 +1531,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1405,7 +1548,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>12</v>
@@ -1435,15 +1578,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1452,7 +1595,7 @@
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -1479,15 +1622,15 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -1496,7 +1639,7 @@
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
@@ -1523,27 +1666,27 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
@@ -1570,21 +1713,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
@@ -1611,15 +1754,15 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -1628,13 +1771,13 @@
         <v>51</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I13" s="3">
         <v>14</v>
@@ -1655,15 +1798,15 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -1672,7 +1815,7 @@
         <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>18</v>
@@ -1699,15 +1842,15 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -1716,7 +1859,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>19</v>
@@ -1740,15 +1883,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -1757,7 +1900,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>20</v>
@@ -1784,41 +1927,47 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>89</v>
+      <c r="H17" s="5" t="s">
+        <v>204</v>
       </c>
       <c r="I17" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1827,27 +1976,33 @@
         <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>90</v>
+      <c r="H18" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="I18" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -1856,27 +2011,48 @@
         <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>91</v>
+      <c r="H19" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="I19" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19" s="1">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>8</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2</v>
+      </c>
+      <c r="M19" s="1">
+        <v>4</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="O19" s="1">
+        <v>5</v>
+      </c>
+      <c r="P19" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -1885,27 +2061,27 @@
         <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I20" s="3">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -1914,27 +2090,27 @@
         <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I21" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -1943,131 +2119,131 @@
         <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I22" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I23" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I24" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I25" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I26" s="3">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -2076,27 +2252,27 @@
         <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I27" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -2105,105 +2281,105 @@
         <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I28" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I29" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I30" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I31" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2212,27 +2388,27 @@
         <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I32" s="3">
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -2241,62 +2417,62 @@
         <v>70</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I33" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I34" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>38</v>
@@ -2308,67 +2484,67 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I36" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I37" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
@@ -2377,7 +2553,7 @@
         <v>75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>41</v>
@@ -2389,15 +2565,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -2406,27 +2582,27 @@
         <v>74</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I39" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -2435,13 +2611,13 @@
         <v>79</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I40" s="3">
         <v>35</v>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A579C577-1B02-4BCC-BD9A-99EB45AF93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D9F424-50BB-4C33-AA0C-867EDB700804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -331,9 +331,6 @@
   </si>
   <si>
     <t>对指定行的第一个目标造成普通攻击{0}%的物理伤害。在下一回合中，该目标无法行动，同时，你优先行动。</t>
-  </si>
-  <si>
-    <t>以指定行的第一个目标为原点，对锥形范围内的所有目标造成{0}点风雷伤害。</t>
   </si>
   <si>
     <t>对任意一个目标造成{0}点治疗。</t>
@@ -784,6 +781,9 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>以指定行的第一个目标为原点，对锥形范围内的所有目标造成{0}。</t>
+  </si>
 </sst>
 </file>
 
@@ -793,7 +793,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -805,7 +805,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -865,7 +865,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -1195,17 +1195,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S40"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="50.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.75" style="3"/>
-    <col min="10" max="16384" width="8.75" style="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="50.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="3"/>
+    <col min="10" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -1213,19 +1213,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1234,37 +1234,37 @@
         <v>2</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="O1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -1272,16 +1272,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
@@ -1293,37 +1293,37 @@
         <v>3</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -1331,7 +1331,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1339,19 +1339,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>6</v>
@@ -1360,37 +1360,37 @@
         <v>7</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1398,16 +1398,16 @@
         <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>9</v>
@@ -1439,10 +1439,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1451,7 +1451,7 @@
         <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
@@ -1483,10 +1483,10 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
@@ -1495,13 +1495,13 @@
         <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I7" s="3">
         <v>14</v>
@@ -1536,10 +1536,10 @@
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1548,7 +1548,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>12</v>
@@ -1583,10 +1583,10 @@
         <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1595,7 +1595,7 @@
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -1627,10 +1627,10 @@
         <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -1639,7 +1639,7 @@
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
@@ -1671,22 +1671,22 @@
         <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
@@ -1718,16 +1718,16 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
@@ -1759,10 +1759,10 @@
         <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -1771,13 +1771,13 @@
         <v>51</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I13" s="3">
         <v>14</v>
@@ -1803,10 +1803,10 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -1815,7 +1815,7 @@
         <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>18</v>
@@ -1847,10 +1847,10 @@
         <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -1859,7 +1859,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>19</v>
@@ -1888,10 +1888,10 @@
         <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -1900,7 +1900,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>20</v>
@@ -1927,27 +1927,27 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I17" s="3">
         <v>1</v>
@@ -1959,15 +1959,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1976,13 +1976,13 @@
         <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I18" s="3">
         <v>7</v>
@@ -1994,15 +1994,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -2011,13 +2011,13 @@
         <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I19" s="3">
         <v>14</v>
@@ -2044,15 +2044,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -2061,7 +2061,7 @@
         <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>24</v>
@@ -2072,16 +2072,31 @@
       <c r="I20" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J20" s="1">
+        <v>22</v>
+      </c>
+      <c r="K20" s="1">
+        <v>76</v>
+      </c>
+      <c r="L20" s="1">
+        <v>10</v>
+      </c>
+      <c r="M20" s="1">
+        <v>31</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -2090,7 +2105,7 @@
         <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
@@ -2101,16 +2116,31 @@
       <c r="I21" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J21" s="1">
+        <v>32</v>
+      </c>
+      <c r="K21" s="1">
+        <v>101</v>
+      </c>
+      <c r="L21" s="1">
+        <v>18</v>
+      </c>
+      <c r="M21" s="1">
+        <v>60</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -2119,7 +2149,7 @@
         <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>26</v>
@@ -2130,22 +2160,28 @@
       <c r="I22" s="3">
         <v>35</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J22" s="1">
+        <v>50</v>
+      </c>
+      <c r="K22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>27</v>
@@ -2156,22 +2192,34 @@
       <c r="I23" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
@@ -2182,22 +2230,28 @@
       <c r="I24" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>29</v>
@@ -2208,22 +2262,52 @@
       <c r="I25" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>4</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
+        <v>2</v>
+      </c>
+      <c r="N25" s="1">
+        <v>4</v>
+      </c>
+      <c r="O25" s="1">
+        <v>8</v>
+      </c>
+      <c r="P25" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>4</v>
+      </c>
+      <c r="R25" s="1">
+        <v>1</v>
+      </c>
+      <c r="S25" s="1">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>30</v>
@@ -2234,16 +2318,28 @@
       <c r="I26" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J26" s="1">
+        <v>5</v>
+      </c>
+      <c r="K26" s="1">
+        <v>9</v>
+      </c>
+      <c r="L26" s="1">
+        <v>3</v>
+      </c>
+      <c r="M26" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -2252,7 +2348,7 @@
         <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>31</v>
@@ -2263,16 +2359,22 @@
       <c r="I27" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J27" s="1">
+        <v>120</v>
+      </c>
+      <c r="K27" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -2281,105 +2383,120 @@
         <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>98</v>
+        <v>206</v>
       </c>
       <c r="I28" s="3">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>135</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
+        <v>71</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I29" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I30" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I31" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2388,13 +2505,13 @@
         <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I32" s="3">
         <v>21</v>
@@ -2405,10 +2522,10 @@
         <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -2417,13 +2534,13 @@
         <v>70</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I33" s="3">
         <v>28</v>
@@ -2434,25 +2551,25 @@
         <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="I34" s="3">
         <v>35</v>
@@ -2463,16 +2580,16 @@
         <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>38</v>
@@ -2489,22 +2606,22 @@
         <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I36" s="3">
         <v>7</v>
@@ -2515,22 +2632,22 @@
         <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I37" s="3">
         <v>14</v>
@@ -2541,10 +2658,10 @@
         <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
@@ -2553,7 +2670,7 @@
         <v>75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>41</v>
@@ -2570,10 +2687,10 @@
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -2582,13 +2699,13 @@
         <v>74</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I39" s="3">
         <v>28</v>
@@ -2599,10 +2716,10 @@
         <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -2611,13 +2728,13 @@
         <v>79</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I40" s="3">
         <v>35</v>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D9F424-50BB-4C33-AA0C-867EDB700804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0912CF-87FA-4919-A5B2-AE158C52ACE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="213">
   <si>
     <t>id</t>
   </si>
@@ -306,9 +306,6 @@
     <t>对除中心点以外的所有目标造成{0}点风雷伤害。</t>
   </si>
   <si>
-    <t>增加{0}%命中。</t>
-  </si>
-  <si>
     <t>对最靠前的一列所有目标造成{0}点物理伤害。</t>
   </si>
   <si>
@@ -333,12 +330,6 @@
     <t>对指定行的第一个目标造成普通攻击{0}%的物理伤害。在下一回合中，该目标无法行动，同时，你优先行动。</t>
   </si>
   <si>
-    <t>对任意一个目标造成{0}点治疗。</t>
-  </si>
-  <si>
-    <t>增加{0}%法术闪避，持续{1}回合。</t>
-  </si>
-  <si>
     <t>隐身{0}回合，使敌人的指向性攻击无法攻击到你，同时，你可以逃跑。</t>
   </si>
   <si>
@@ -351,21 +342,6 @@
     <t>神圣责罚</t>
   </si>
   <si>
-    <t>使目标在3回合后受到{0}点神圣伤害。</t>
-  </si>
-  <si>
-    <t>施展装备的毒囊的效果，持续{0}回合，若未装备任何毒囊，则造成{1}点毒素伤害。</t>
-  </si>
-  <si>
-    <t>召唤一个生命值{0}，物理攻击{1)的骷髅为你作战，最多{2}个骷髅。</t>
-  </si>
-  <si>
-    <t>使攻击附加{0}点神圣伤害，并对妖魔增伤{1}%。</t>
-  </si>
-  <si>
-    <t>召唤一个生命值{0}，火焰攻击{1)的神兽为你作战，神兽可攻击2格目标。</t>
-  </si>
-  <si>
     <t>level</t>
   </si>
   <si>
@@ -417,36 +393,6 @@
     <t>Enum:SkillTag[]</t>
   </si>
   <si>
-    <t>fire</t>
-  </si>
-  <si>
-    <t>thunder</t>
-  </si>
-  <si>
-    <t>battle</t>
-  </si>
-  <si>
-    <t>holy</t>
-  </si>
-  <si>
-    <t>xskill</t>
-  </si>
-  <si>
-    <t>thunder,summon</t>
-  </si>
-  <si>
-    <t>thunder,guardian</t>
-  </si>
-  <si>
-    <t>battle,fire</t>
-  </si>
-  <si>
-    <t>xskill,thunder</t>
-  </si>
-  <si>
-    <t>holy,guardian</t>
-  </si>
-  <si>
     <t>posx</t>
   </si>
   <si>
@@ -577,18 +523,6 @@
   </si>
   <si>
     <t>hhel,hlok</t>
-  </si>
-  <si>
-    <t>psyco,battle</t>
-  </si>
-  <si>
-    <t>psyco,summon</t>
-  </si>
-  <si>
-    <t>psyco,fire</t>
-  </si>
-  <si>
-    <t>psyco,poison</t>
   </si>
   <si>
     <t>n1</t>
@@ -783,6 +717,90 @@
   </si>
   <si>
     <t>以指定行的第一个目标为原点，对锥形范围内的所有目标造成{0}。</t>
+  </si>
+  <si>
+    <t>skmage,fire,fdmg</t>
+  </si>
+  <si>
+    <t>skmage,thunder,summon,luck</t>
+  </si>
+  <si>
+    <t>skmage,thunder,tdmg</t>
+  </si>
+  <si>
+    <t>skmage,thunder,guardian</t>
+  </si>
+  <si>
+    <t>skwarr,battle</t>
+  </si>
+  <si>
+    <t>skwarr,battle,xdmg</t>
+  </si>
+  <si>
+    <t>skwarr,battle,fire,xdmg,fdmg</t>
+  </si>
+  <si>
+    <t>skwarr,xskill</t>
+  </si>
+  <si>
+    <t>skwarr,xskill,xdmg</t>
+  </si>
+  <si>
+    <t>skwarr,xskill,thunder,xdmg,tdmg</t>
+  </si>
+  <si>
+    <t>skwlok,holy,heal</t>
+  </si>
+  <si>
+    <t>skwlok,holy,guardian</t>
+  </si>
+  <si>
+    <t>skwlok,holy</t>
+  </si>
+  <si>
+    <t>skwlok,holy,hdmg</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,battle</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,poison,pdmg</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,summon</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,fire,fdmg</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,battle,hdmg</t>
+  </si>
+  <si>
+    <t>对任意一个目标造成{0}。</t>
+  </si>
+  <si>
+    <t>增加{0.2}%法术闪避，持续{1}回合。</t>
+  </si>
+  <si>
+    <t>使目标在{0}回合后受到{1}。</t>
+  </si>
+  <si>
+    <t>增加{0.2}%命中。</t>
+  </si>
+  <si>
+    <t>造成{0}，持续{1}回合。</t>
+  </si>
+  <si>
+    <t>召唤一个生命值{0}，可以造成{1}的骷髅为你作战，最多{2}个骷髅。</t>
+  </si>
+  <si>
+    <t>使攻击附加{0}，并对妖魔增伤{1.2}%。</t>
+  </si>
+  <si>
+    <t>对指定行的第一个目标造成{0}。</t>
+  </si>
+  <si>
+    <t>召唤一个生命值{0}，可以造成{1}的神兽为你作战，神兽可攻击{2}格目标。</t>
   </si>
 </sst>
 </file>
@@ -1213,19 +1231,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1234,37 +1252,37 @@
         <v>2</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -1272,16 +1290,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
@@ -1293,37 +1311,37 @@
         <v>3</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -1331,7 +1349,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1339,19 +1357,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>6</v>
@@ -1360,37 +1378,37 @@
         <v>7</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1398,16 +1416,16 @@
         <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>9</v>
@@ -1439,10 +1457,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1451,7 +1469,7 @@
         <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
@@ -1483,10 +1501,10 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
@@ -1495,13 +1513,13 @@
         <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="I7" s="3">
         <v>14</v>
@@ -1536,10 +1554,10 @@
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1548,7 +1566,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>12</v>
@@ -1583,10 +1601,10 @@
         <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1595,7 +1613,7 @@
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -1627,10 +1645,10 @@
         <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -1639,7 +1657,7 @@
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
@@ -1671,22 +1689,22 @@
         <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
@@ -1718,16 +1736,16 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
@@ -1759,10 +1777,10 @@
         <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -1771,13 +1789,13 @@
         <v>51</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="I13" s="3">
         <v>14</v>
@@ -1803,10 +1821,10 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -1815,7 +1833,7 @@
         <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>18</v>
@@ -1847,10 +1865,10 @@
         <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -1859,7 +1877,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>19</v>
@@ -1888,10 +1906,10 @@
         <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -1900,7 +1918,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>20</v>
@@ -1932,22 +1950,22 @@
         <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="I17" s="3">
         <v>1</v>
@@ -1964,10 +1982,10 @@
         <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1976,13 +1994,13 @@
         <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="I18" s="3">
         <v>7</v>
@@ -1999,10 +2017,10 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -2011,13 +2029,13 @@
         <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I19" s="3">
         <v>14</v>
@@ -2049,10 +2067,10 @@
         <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -2061,13 +2079,13 @@
         <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I20" s="3">
         <v>21</v>
@@ -2093,10 +2111,10 @@
         <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -2105,13 +2123,13 @@
         <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I21" s="3">
         <v>28</v>
@@ -2137,10 +2155,10 @@
         <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -2149,13 +2167,13 @@
         <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I22" s="3">
         <v>35</v>
@@ -2172,22 +2190,22 @@
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I23" s="3">
         <v>1</v>
@@ -2210,22 +2228,22 @@
         <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I24" s="3">
         <v>7</v>
@@ -2242,22 +2260,22 @@
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I25" s="3">
         <v>14</v>
@@ -2298,22 +2316,22 @@
         <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I26" s="3">
         <v>21</v>
@@ -2336,10 +2354,10 @@
         <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -2348,13 +2366,13 @@
         <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I27" s="3">
         <v>28</v>
@@ -2371,10 +2389,10 @@
         <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -2383,13 +2401,13 @@
         <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="I28" s="3">
         <v>35</v>
@@ -2415,25 +2433,37 @@
         <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>98</v>
+        <v>204</v>
       </c>
       <c r="I29" s="3">
         <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>5</v>
+      </c>
+      <c r="K29" s="1">
+        <v>10</v>
+      </c>
+      <c r="L29" s="1">
+        <v>2</v>
+      </c>
+      <c r="M29" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -2441,25 +2471,37 @@
         <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="I30" s="3">
         <v>7</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L30" s="1">
+        <v>3</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0.35</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -2467,25 +2509,31 @@
         <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I31" s="3">
         <v>14</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -2493,10 +2541,10 @@
         <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2505,27 +2553,39 @@
         <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I32" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="1">
+        <v>20</v>
+      </c>
+      <c r="K32" s="1">
+        <v>35</v>
+      </c>
+      <c r="L32" s="1">
+        <v>11</v>
+      </c>
+      <c r="M32" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -2534,134 +2594,206 @@
         <v>70</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I33" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>10</v>
+      </c>
+      <c r="M33" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="I34" s="3">
         <v>35</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="1">
+        <v>3</v>
+      </c>
+      <c r="K34" s="1">
+        <v>300</v>
+      </c>
+      <c r="L34" s="1">
+        <v>155</v>
+      </c>
+      <c r="M34" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>89</v>
+        <v>207</v>
       </c>
       <c r="I35" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="I36" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>10</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>5</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="O36" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="I37" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" s="1">
+        <v>100</v>
+      </c>
+      <c r="K37" s="1">
+        <v>75</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
+        <v>2</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="O37" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="P37" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
@@ -2670,27 +2802,42 @@
         <v>75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="I38" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" s="1">
+        <v>54</v>
+      </c>
+      <c r="K38" s="1">
+        <v>190</v>
+      </c>
+      <c r="L38" s="1">
+        <v>27</v>
+      </c>
+      <c r="M38" s="1">
+        <v>95</v>
+      </c>
+      <c r="N38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -2699,27 +2846,42 @@
         <v>74</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>107</v>
+        <v>210</v>
       </c>
       <c r="I39" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" s="1">
+        <v>114</v>
+      </c>
+      <c r="K39" s="1">
+        <v>63</v>
+      </c>
+      <c r="L39" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M39" s="1">
+        <v>50</v>
+      </c>
+      <c r="N39" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -2728,16 +2890,37 @@
         <v>79</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>108</v>
+        <v>212</v>
       </c>
       <c r="I40" s="3">
         <v>35</v>
+      </c>
+      <c r="J40" s="1">
+        <v>350</v>
+      </c>
+      <c r="K40" s="1">
+        <v>180</v>
+      </c>
+      <c r="L40" s="1">
+        <v>44</v>
+      </c>
+      <c r="M40" s="1">
+        <v>72</v>
+      </c>
+      <c r="N40" s="1">
+        <v>21</v>
+      </c>
+      <c r="O40" s="1">
+        <v>30</v>
+      </c>
+      <c r="P40" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0912CF-87FA-4919-A5B2-AE158C52ACE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8400DD06-5738-4F83-85B8-A4C14BBF39A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="212">
   <si>
     <t>id</t>
   </si>
@@ -279,33 +279,9 @@
     <t>pskl</t>
   </si>
   <si>
-    <t>对指定行的第一个目标造成{0}点火焰伤害。</t>
-  </si>
-  <si>
-    <t>对第一列所有目标造成{0}点火焰伤害，并使其在当前回合无法攻击。</t>
-  </si>
-  <si>
-    <t>对指定行的第一个目标造成{0}点火焰伤害，并对{1}个临近目标造成全额伤害。</t>
-  </si>
-  <si>
-    <t>随机对6个目标造成{0}点火焰伤害，一定会选中被点燃的目标。</t>
-  </si>
-  <si>
-    <t>对指定2x2范围施展火墙，每回合对该格内的目标造成{0}点火焰伤害，持续3回合。</t>
-  </si>
-  <si>
-    <t>对任意一个目标造成{0}点风雷伤害。</t>
-  </si>
-  <si>
-    <t>对指定2行或者2列的所有目标造成{0}点风雷伤害。</t>
-  </si>
-  <si>
     <t>提升物理抗性{0}%，持续{1}回合。</t>
   </si>
   <si>
-    <t>对除中心点以外的所有目标造成{0}点风雷伤害。</t>
-  </si>
-  <si>
     <t>对最靠前的一列所有目标造成{0}点物理伤害。</t>
   </si>
   <si>
@@ -574,12 +550,6 @@
   </si>
   <si>
     <t>有{0.2}%的概率使目标敌人加入你的队伍，最多诱惑{1}个敌人，无法对精英和Boss施放。每{2}点运气可提升1%成功率。</t>
-  </si>
-  <si>
-    <t>对指定行所有目标造成{0}点风雷伤害，法术命中-20%。</t>
-  </si>
-  <si>
-    <t>对任意一个目标造成{0}点火焰伤害并造成{1}回合的点燃效果，并且每回合会引燃临近的{2}个目标。</t>
   </si>
   <si>
     <r>
@@ -801,6 +771,33 @@
   </si>
   <si>
     <t>召唤一个生命值{0}，可以造成{1}的神兽为你作战，神兽可攻击{2}格目标。</t>
+  </si>
+  <si>
+    <t>对第一列所有目标造成{0}，并使其在当前回合无法攻击。</t>
+  </si>
+  <si>
+    <t>对任意一个目标造成{0}害并造成{1}回合的点燃效果，并且每回合会引燃临近的{2}个目标。</t>
+  </si>
+  <si>
+    <t>对指定行的第一个目标造成{0}，并对{1}个临近目标造成全额伤害。</t>
+  </si>
+  <si>
+    <t>随机对6个目标造成{0}，一定会选中被点燃的目标。</t>
+  </si>
+  <si>
+    <t>对指定2x2范围施展火墙，每回合对该格内的目标造成{0}，持续{1}回合。</t>
+  </si>
+  <si>
+    <t>对指定任意一个目标造成{0}。</t>
+  </si>
+  <si>
+    <t>对指定行所有目标造成{0}，法术命中-20%。</t>
+  </si>
+  <si>
+    <t>对指定2行或者2列的所有目标造成{0}。</t>
+  </si>
+  <si>
+    <t>对除中心点以外的所有目标造成{0}。</t>
   </si>
 </sst>
 </file>
@@ -1231,19 +1228,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1252,37 +1249,37 @@
         <v>2</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -1290,16 +1287,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
@@ -1311,37 +1308,37 @@
         <v>3</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -1349,7 +1346,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1357,19 +1354,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>6</v>
@@ -1378,37 +1375,37 @@
         <v>7</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="R4" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1416,22 +1413,22 @@
         <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -1457,10 +1454,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1469,13 +1466,13 @@
         <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="I6" s="3">
         <v>7</v>
@@ -1501,10 +1498,10 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
@@ -1513,13 +1510,13 @@
         <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="I7" s="3">
         <v>14</v>
@@ -1554,10 +1551,10 @@
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1566,13 +1563,13 @@
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="I8" s="3">
         <v>21</v>
@@ -1601,10 +1598,10 @@
         <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1613,13 +1610,13 @@
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="I9" s="3">
         <v>28</v>
@@ -1645,10 +1642,10 @@
         <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -1657,13 +1654,13 @@
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="I10" s="3">
         <v>35</v>
@@ -1682,6 +1679,9 @@
       </c>
       <c r="N10" s="1">
         <v>1.1000000000000001</v>
+      </c>
+      <c r="O10" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1689,22 +1689,22 @@
         <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
@@ -1736,22 +1736,22 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="I12" s="3">
         <v>7</v>
@@ -1777,10 +1777,10 @@
         <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -1789,13 +1789,13 @@
         <v>51</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I13" s="3">
         <v>14</v>
@@ -1821,10 +1821,10 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -1833,13 +1833,13 @@
         <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="I14" s="3">
         <v>21</v>
@@ -1865,10 +1865,10 @@
         <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -1877,13 +1877,13 @@
         <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I15" s="3">
         <v>28</v>
@@ -1906,10 +1906,10 @@
         <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -1918,13 +1918,13 @@
         <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="I16" s="3">
         <v>35</v>
@@ -1950,22 +1950,22 @@
         <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="I17" s="3">
         <v>1</v>
@@ -1982,10 +1982,10 @@
         <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1994,13 +1994,13 @@
         <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I18" s="3">
         <v>7</v>
@@ -2017,10 +2017,10 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -2029,13 +2029,13 @@
         <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I19" s="3">
         <v>14</v>
@@ -2067,10 +2067,10 @@
         <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -2079,13 +2079,13 @@
         <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I20" s="3">
         <v>21</v>
@@ -2111,10 +2111,10 @@
         <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -2123,13 +2123,13 @@
         <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I21" s="3">
         <v>28</v>
@@ -2155,10 +2155,10 @@
         <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -2167,13 +2167,13 @@
         <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I22" s="3">
         <v>35</v>
@@ -2190,22 +2190,22 @@
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I23" s="3">
         <v>1</v>
@@ -2228,22 +2228,22 @@
         <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I24" s="3">
         <v>7</v>
@@ -2260,22 +2260,22 @@
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I25" s="3">
         <v>14</v>
@@ -2316,22 +2316,22 @@
         <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I26" s="3">
         <v>21</v>
@@ -2354,10 +2354,10 @@
         <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -2366,13 +2366,13 @@
         <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I27" s="3">
         <v>28</v>
@@ -2389,10 +2389,10 @@
         <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -2401,13 +2401,13 @@
         <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="I28" s="3">
         <v>35</v>
@@ -2433,22 +2433,22 @@
         <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I29" s="3">
         <v>1</v>
@@ -2471,22 +2471,22 @@
         <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="I30" s="3">
         <v>7</v>
@@ -2509,22 +2509,22 @@
         <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="I31" s="3">
         <v>14</v>
@@ -2541,10 +2541,10 @@
         <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2553,13 +2553,13 @@
         <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I32" s="3">
         <v>21</v>
@@ -2582,10 +2582,10 @@
         <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -2594,13 +2594,13 @@
         <v>70</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="I33" s="3">
         <v>28</v>
@@ -2623,25 +2623,25 @@
         <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="I34" s="3">
         <v>35</v>
@@ -2664,22 +2664,22 @@
         <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="I35" s="3">
         <v>1</v>
@@ -2696,22 +2696,22 @@
         <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="I36" s="3">
         <v>7</v>
@@ -2740,22 +2740,22 @@
         <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="I37" s="3">
         <v>14</v>
@@ -2790,10 +2790,10 @@
         <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
@@ -2802,13 +2802,13 @@
         <v>75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="I38" s="3">
         <v>21</v>
@@ -2834,10 +2834,10 @@
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -2846,13 +2846,13 @@
         <v>74</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I39" s="3">
         <v>28</v>
@@ -2878,10 +2878,10 @@
         <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -2890,13 +2890,13 @@
         <v>79</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="I40" s="3">
         <v>35</v>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8400DD06-5738-4F83-85B8-A4C14BBF39A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D20436-08DD-4457-A153-39C102F3C91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -286,9 +286,6 @@
   </si>
   <si>
     <t>对任意目标及其十字范围内的所有目标造成{0}点物理伤害。</t>
-  </si>
-  <si>
-    <t>对指定行的第一个目标造成一次普通攻击并附加{0}%的火焰伤害。</t>
   </si>
   <si>
     <t>增加{0}点物理减免。</t>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t>对除中心点以外的所有目标造成{0}。</t>
+  </si>
+  <si>
+    <t>对指定行的第一个目标造成一次普通攻击并附加{0}。</t>
   </si>
 </sst>
 </file>
@@ -1228,19 +1228,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1249,37 +1249,37 @@
         <v>2</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="O1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -1287,16 +1287,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
@@ -1308,37 +1308,37 @@
         <v>3</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -1346,7 +1346,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1354,19 +1354,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>6</v>
@@ -1375,37 +1375,37 @@
         <v>7</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1413,22 +1413,22 @@
         <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -1454,10 +1454,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1466,13 +1466,13 @@
         <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I6" s="3">
         <v>7</v>
@@ -1498,10 +1498,10 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
@@ -1510,13 +1510,13 @@
         <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I7" s="3">
         <v>14</v>
@@ -1551,10 +1551,10 @@
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1563,13 +1563,13 @@
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I8" s="3">
         <v>21</v>
@@ -1598,10 +1598,10 @@
         <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1610,13 +1610,13 @@
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I9" s="3">
         <v>28</v>
@@ -1642,10 +1642,10 @@
         <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -1654,13 +1654,13 @@
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I10" s="3">
         <v>35</v>
@@ -1689,22 +1689,22 @@
         <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
@@ -1736,22 +1736,22 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I12" s="3">
         <v>7</v>
@@ -1777,10 +1777,10 @@
         <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -1789,13 +1789,13 @@
         <v>51</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I13" s="3">
         <v>14</v>
@@ -1821,10 +1821,10 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -1833,13 +1833,13 @@
         <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I14" s="3">
         <v>21</v>
@@ -1865,10 +1865,10 @@
         <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -1877,7 +1877,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>19</v>
@@ -1906,10 +1906,10 @@
         <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -1918,13 +1918,13 @@
         <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I16" s="3">
         <v>35</v>
@@ -1950,22 +1950,22 @@
         <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I17" s="3">
         <v>1</v>
@@ -1982,10 +1982,10 @@
         <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1994,13 +1994,13 @@
         <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I18" s="3">
         <v>7</v>
@@ -2017,10 +2017,10 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -2029,13 +2029,13 @@
         <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I19" s="3">
         <v>14</v>
@@ -2067,10 +2067,10 @@
         <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -2079,7 +2079,7 @@
         <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>24</v>
@@ -2111,10 +2111,10 @@
         <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -2123,7 +2123,7 @@
         <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
@@ -2155,10 +2155,10 @@
         <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -2167,13 +2167,13 @@
         <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="I22" s="3">
         <v>35</v>
@@ -2190,22 +2190,22 @@
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I23" s="3">
         <v>1</v>
@@ -2228,22 +2228,22 @@
         <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I24" s="3">
         <v>7</v>
@@ -2260,22 +2260,22 @@
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I25" s="3">
         <v>14</v>
@@ -2316,22 +2316,22 @@
         <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I26" s="3">
         <v>21</v>
@@ -2354,10 +2354,10 @@
         <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -2366,13 +2366,13 @@
         <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I27" s="3">
         <v>28</v>
@@ -2389,10 +2389,10 @@
         <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -2401,13 +2401,13 @@
         <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I28" s="3">
         <v>35</v>
@@ -2433,22 +2433,22 @@
         <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I29" s="3">
         <v>1</v>
@@ -2471,22 +2471,22 @@
         <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I30" s="3">
         <v>7</v>
@@ -2509,22 +2509,22 @@
         <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I31" s="3">
         <v>14</v>
@@ -2541,10 +2541,10 @@
         <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2553,13 +2553,13 @@
         <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I32" s="3">
         <v>21</v>
@@ -2582,10 +2582,10 @@
         <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -2594,13 +2594,13 @@
         <v>70</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I33" s="3">
         <v>28</v>
@@ -2623,25 +2623,25 @@
         <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I34" s="3">
         <v>35</v>
@@ -2664,22 +2664,22 @@
         <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I35" s="3">
         <v>1</v>
@@ -2696,22 +2696,22 @@
         <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I36" s="3">
         <v>7</v>
@@ -2740,22 +2740,22 @@
         <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I37" s="3">
         <v>14</v>
@@ -2790,10 +2790,10 @@
         <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
@@ -2802,13 +2802,13 @@
         <v>75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I38" s="3">
         <v>21</v>
@@ -2834,10 +2834,10 @@
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -2846,13 +2846,13 @@
         <v>74</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I39" s="3">
         <v>28</v>
@@ -2878,10 +2878,10 @@
         <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -2890,13 +2890,13 @@
         <v>79</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I40" s="3">
         <v>35</v>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D20436-08DD-4457-A153-39C102F3C91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DF3A7E-DE3B-4B43-989B-F10F7595BC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5510" yWindow="3710" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="217">
   <si>
     <t>id</t>
   </si>
@@ -798,6 +798,21 @@
   </si>
   <si>
     <t>对指定行的第一个目标造成一次普通攻击并附加{0}。</t>
+  </si>
+  <si>
+    <t>bele</t>
+  </si>
+  <si>
+    <t>skwarr,battle,fdmg,tdmg,hdmg,pdmg</t>
+  </si>
+  <si>
+    <t>Ability_Warrior_WeaponMastery</t>
+  </si>
+  <si>
+    <t>元素剑术</t>
+  </si>
+  <si>
+    <t>使你的所有攻击能附带{0.2}%的元素伤害。当前增加{1}。</t>
   </si>
 </sst>
 </file>
@@ -1209,21 +1224,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S40"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="50.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="3"/>
-    <col min="10" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="6" width="14.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="50.81640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="3"/>
+    <col min="10" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +1297,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,7 +1356,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1349,7 +1364,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1408,7 +1423,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
@@ -1449,7 +1464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -1493,7 +1508,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1546,7 +1561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
@@ -1593,7 +1608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1637,7 +1652,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
@@ -1684,7 +1699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -1731,7 +1746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
@@ -1772,7 +1787,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
@@ -1816,7 +1831,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1860,7 +1875,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
@@ -1901,7 +1916,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
@@ -1945,7 +1960,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1977,7 +1992,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>57</v>
       </c>
@@ -2012,7 +2027,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
@@ -2062,53 +2077,44 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="15" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="D20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>81</v>
+        <v>215</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="I20" s="3">
         <v>21</v>
       </c>
       <c r="J20" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1">
-        <v>76</v>
-      </c>
-      <c r="L20" s="1">
-        <v>10</v>
-      </c>
-      <c r="M20" s="1">
-        <v>31</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>102</v>
@@ -2120,112 +2126,115 @@
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I21" s="3">
         <v>28</v>
       </c>
       <c r="J21" s="1">
+        <v>22</v>
+      </c>
+      <c r="K21" s="1">
+        <v>76</v>
+      </c>
+      <c r="L21" s="1">
+        <v>10</v>
+      </c>
+      <c r="M21" s="1">
+        <v>31</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="3">
+        <v>28</v>
+      </c>
+      <c r="J22" s="1">
         <v>32</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K22" s="1">
         <v>101</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L22" s="1">
         <v>18</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M22" s="1">
         <v>60</v>
       </c>
-      <c r="N21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="N22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I22" s="3">
-        <v>35</v>
-      </c>
-      <c r="J22" s="1">
-        <v>50</v>
-      </c>
-      <c r="K22" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
+      <c r="E23" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="F23" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="I23" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J23" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="K23" s="1">
-        <v>4</v>
-      </c>
-      <c r="L23" s="1">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>102</v>
@@ -2237,689 +2246,727 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I24" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I25" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1">
-        <v>4</v>
-      </c>
-      <c r="L25" s="1">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1">
-        <v>2</v>
-      </c>
-      <c r="N25" s="1">
-        <v>4</v>
-      </c>
-      <c r="O25" s="1">
-        <v>8</v>
-      </c>
-      <c r="P25" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>4</v>
-      </c>
-      <c r="R25" s="1">
-        <v>1</v>
-      </c>
-      <c r="S25" s="1">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I26" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J26" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K26" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L26" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M26" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="N26" s="1">
+        <v>4</v>
+      </c>
+      <c r="O26" s="1">
+        <v>8</v>
+      </c>
+      <c r="P26" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>4</v>
+      </c>
+      <c r="R26" s="1">
+        <v>1</v>
+      </c>
+      <c r="S26" s="1">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I27" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J27" s="1">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="K27" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="L27" s="1">
+        <v>3</v>
+      </c>
+      <c r="M27" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I28" s="3">
+        <v>28</v>
+      </c>
+      <c r="J28" s="1">
+        <v>120</v>
+      </c>
+      <c r="K28" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="I28" s="3">
+      <c r="I29" s="3">
         <v>35</v>
       </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
         <v>135</v>
       </c>
-      <c r="L28" s="1">
-        <v>1</v>
-      </c>
-      <c r="M28" s="1">
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
         <v>71</v>
       </c>
-      <c r="N28" s="1">
+      <c r="N29" s="1">
         <v>1.3</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I29" s="3">
-        <v>1</v>
-      </c>
-      <c r="J29" s="1">
-        <v>5</v>
-      </c>
-      <c r="K29" s="1">
-        <v>10</v>
-      </c>
-      <c r="L29" s="1">
-        <v>2</v>
-      </c>
-      <c r="M29" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D30" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I30" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J30" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K30" s="1">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="L30" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" s="1">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D31" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="I31" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J31" s="1">
         <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="L31" s="1">
+        <v>3</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D32" s="1">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I32" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J32" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>35</v>
-      </c>
-      <c r="L32" s="1">
-        <v>11</v>
-      </c>
-      <c r="M32" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D33" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I33" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J33" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K33" s="1">
-        <v>0.1</v>
+        <v>35</v>
       </c>
       <c r="L33" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M33" s="1">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D34" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>195</v>
+        <v>90</v>
       </c>
       <c r="I34" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J34" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34" s="1">
-        <v>300</v>
+        <v>0.1</v>
       </c>
       <c r="L34" s="1">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="M34" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
+      <c r="E35" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F35" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I35" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J35" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="L35" s="1">
+        <v>155</v>
+      </c>
+      <c r="M35" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D36" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I36" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1">
-        <v>10</v>
-      </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
-        <v>5</v>
-      </c>
-      <c r="N36" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="O36" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D37" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I37" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="L37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N37" s="1">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="O37" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="P37" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I38" s="3">
+        <v>14</v>
+      </c>
+      <c r="J38" s="1">
+        <v>100</v>
+      </c>
+      <c r="K38" s="1">
+        <v>75</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1">
         <v>2</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I38" s="3">
-        <v>21</v>
-      </c>
-      <c r="J38" s="1">
-        <v>54</v>
-      </c>
-      <c r="K38" s="1">
-        <v>190</v>
-      </c>
-      <c r="L38" s="1">
-        <v>27</v>
-      </c>
-      <c r="M38" s="1">
-        <v>95</v>
-      </c>
       <c r="N38" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="P38" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I39" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J39" s="1">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="K39" s="1">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="L39" s="1">
-        <v>2.2000000000000002</v>
+        <v>27</v>
       </c>
       <c r="M39" s="1">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="N39" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I40" s="3">
+        <v>28</v>
+      </c>
+      <c r="J40" s="1">
+        <v>114</v>
+      </c>
+      <c r="K40" s="1">
+        <v>63</v>
+      </c>
+      <c r="L40" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M40" s="1">
+        <v>50</v>
+      </c>
+      <c r="N40" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D41" s="1">
         <v>3</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I40" s="3">
+      <c r="I41" s="3">
         <v>35</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J41" s="1">
         <v>350</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K41" s="1">
         <v>180</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L41" s="1">
         <v>44</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M41" s="1">
         <v>72</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N41" s="1">
         <v>21</v>
       </c>
-      <c r="O40" s="1">
+      <c r="O41" s="1">
         <v>30</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P41" s="1">
         <v>2</v>
       </c>
     </row>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DF3A7E-DE3B-4B43-989B-F10F7595BC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98BFB81-E718-4AC6-B1EE-34779AE24AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5510" yWindow="3710" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18610" yWindow="0" windowWidth="19880" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="227">
   <si>
     <t>id</t>
   </si>
@@ -282,9 +282,6 @@
     <t>提升物理抗性{0}%，持续{1}回合。</t>
   </si>
   <si>
-    <t>对最靠前的一列所有目标造成{0}点物理伤害。</t>
-  </si>
-  <si>
     <t>对任意目标及其十字范围内的所有目标造成{0}点物理伤害。</t>
   </si>
   <si>
@@ -294,13 +291,7 @@
     <t>增加{0}%闪避。</t>
   </si>
   <si>
-    <t>降低{0}点物理减免，并增加{1}点物理伤害，持续{2}回合。</t>
-  </si>
-  <si>
     <t>增加{0}点火焰、风雷、神圣、毒素减免。</t>
-  </si>
-  <si>
-    <t>对指定行的第一个目标造成普通攻击{0}%的物理伤害。在下一回合中，该目标无法行动，同时，你优先行动。</t>
   </si>
   <si>
     <t>隐身{0}回合，使敌人的指向性攻击无法攻击到你，同时，你可以逃跑。</t>
@@ -611,6 +602,150 @@
       <t>暴击几率。</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>以指定行的第一个目标为原点，对锥形范围内的所有目标造成{0}。</t>
+  </si>
+  <si>
+    <t>skmage,fire,fdmg</t>
+  </si>
+  <si>
+    <t>skmage,thunder,summon,luck</t>
+  </si>
+  <si>
+    <t>skmage,thunder,tdmg</t>
+  </si>
+  <si>
+    <t>skmage,thunder,guardian</t>
+  </si>
+  <si>
+    <t>skwarr,battle</t>
+  </si>
+  <si>
+    <t>skwarr,battle,xdmg</t>
+  </si>
+  <si>
+    <t>skwarr,battle,fire,xdmg,fdmg</t>
+  </si>
+  <si>
+    <t>skwarr,xskill</t>
+  </si>
+  <si>
+    <t>skwarr,xskill,xdmg</t>
+  </si>
+  <si>
+    <t>skwarr,xskill,thunder,xdmg,tdmg</t>
+  </si>
+  <si>
+    <t>skwlok,holy,heal</t>
+  </si>
+  <si>
+    <t>skwlok,holy,guardian</t>
+  </si>
+  <si>
+    <t>skwlok,holy</t>
+  </si>
+  <si>
+    <t>skwlok,holy,hdmg</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,battle</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,poison,pdmg</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,summon</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,fire,fdmg</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,battle,hdmg</t>
+  </si>
+  <si>
+    <t>对任意一个目标造成{0}。</t>
+  </si>
+  <si>
+    <t>增加{0.2}%法术闪避，持续{1}回合。</t>
+  </si>
+  <si>
+    <t>使目标在{0}回合后受到{1}。</t>
+  </si>
+  <si>
+    <t>增加{0.2}%命中。</t>
+  </si>
+  <si>
+    <t>造成{0}，持续{1}回合。</t>
+  </si>
+  <si>
+    <t>召唤一个生命值{0}，可以造成{1}的骷髅为你作战，最多{2}个骷髅。</t>
+  </si>
+  <si>
+    <t>使攻击附加{0}，并对妖魔增伤{1.2}%。</t>
+  </si>
+  <si>
+    <t>对指定行的第一个目标造成{0}。</t>
+  </si>
+  <si>
+    <t>召唤一个生命值{0}，可以造成{1}的神兽为你作战，神兽可攻击{2}格目标。</t>
+  </si>
+  <si>
+    <t>对第一列所有目标造成{0}，并使其在当前回合无法攻击。</t>
+  </si>
+  <si>
+    <t>对任意一个目标造成{0}害并造成{1}回合的点燃效果，并且每回合会引燃临近的{2}个目标。</t>
+  </si>
+  <si>
+    <t>对指定行的第一个目标造成{0}，并对{1}个临近目标造成全额伤害。</t>
+  </si>
+  <si>
+    <t>随机对6个目标造成{0}，一定会选中被点燃的目标。</t>
+  </si>
+  <si>
+    <t>对指定2x2范围施展火墙，每回合对该格内的目标造成{0}，持续{1}回合。</t>
+  </si>
+  <si>
+    <t>对指定任意一个目标造成{0}。</t>
+  </si>
+  <si>
+    <t>对指定行所有目标造成{0}，法术命中-20%。</t>
+  </si>
+  <si>
+    <t>对指定2行或者2列的所有目标造成{0}。</t>
+  </si>
+  <si>
+    <t>对除中心点以外的所有目标造成{0}。</t>
+  </si>
+  <si>
+    <t>bele</t>
+  </si>
+  <si>
+    <t>skwarr,battle,fdmg,tdmg,hdmg,pdmg</t>
+  </si>
+  <si>
+    <t>Ability_Warrior_WeaponMastery</t>
+  </si>
+  <si>
+    <t>元素剑术</t>
+  </si>
+  <si>
+    <t>使你的所有攻击能附带{0.2}%的元素伤害。当前增加{1}。</t>
+  </si>
+  <si>
+    <t>xpos</t>
+  </si>
+  <si>
+    <t>Spell_Holy_GreaterBlessingofKings</t>
+  </si>
+  <si>
+    <t>镇魂拳法</t>
+  </si>
+  <si>
+    <t>对任意指定目标造成{0}，并使其在接下来的{1}回合中无法施法。</t>
+  </si>
+  <si>
+    <t>对指定行的第一个目标造成一次普通攻击并附加普通攻击{0.2}%的火焰伤害。当前增加{1}。</t>
   </si>
   <si>
     <r>
@@ -659,7 +794,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>点物理伤害，并对第二目标增伤</t>
+      <t>，并对第二目标增伤</t>
     </r>
     <r>
       <rPr>
@@ -680,139 +815,33 @@
       </rPr>
       <t>。</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>以指定行的第一个目标为原点，对锥形范围内的所有目标造成{0}。</t>
-  </si>
-  <si>
-    <t>skmage,fire,fdmg</t>
-  </si>
-  <si>
-    <t>skmage,thunder,summon,luck</t>
-  </si>
-  <si>
-    <t>skmage,thunder,tdmg</t>
-  </si>
-  <si>
-    <t>skmage,thunder,guardian</t>
-  </si>
-  <si>
-    <t>skwarr,battle</t>
-  </si>
-  <si>
-    <t>skwarr,battle,xdmg</t>
-  </si>
-  <si>
-    <t>skwarr,battle,fire,xdmg,fdmg</t>
-  </si>
-  <si>
-    <t>skwarr,xskill</t>
-  </si>
-  <si>
-    <t>skwarr,xskill,xdmg</t>
-  </si>
-  <si>
-    <t>skwarr,xskill,thunder,xdmg,tdmg</t>
-  </si>
-  <si>
-    <t>skwlok,holy,heal</t>
-  </si>
-  <si>
-    <t>skwlok,holy,guardian</t>
-  </si>
-  <si>
-    <t>skwlok,holy</t>
-  </si>
-  <si>
-    <t>skwlok,holy,hdmg</t>
-  </si>
-  <si>
-    <t>skwlok,psyco,battle</t>
-  </si>
-  <si>
-    <t>skwlok,psyco,poison,pdmg</t>
-  </si>
-  <si>
-    <t>skwlok,psyco,summon</t>
-  </si>
-  <si>
-    <t>skwlok,psyco,fire,fdmg</t>
-  </si>
-  <si>
-    <t>skwlok,psyco,battle,hdmg</t>
-  </si>
-  <si>
-    <t>对任意一个目标造成{0}。</t>
-  </si>
-  <si>
-    <t>增加{0.2}%法术闪避，持续{1}回合。</t>
-  </si>
-  <si>
-    <t>使目标在{0}回合后受到{1}。</t>
-  </si>
-  <si>
-    <t>增加{0.2}%命中。</t>
-  </si>
-  <si>
-    <t>造成{0}，持续{1}回合。</t>
-  </si>
-  <si>
-    <t>召唤一个生命值{0}，可以造成{1}的骷髅为你作战，最多{2}个骷髅。</t>
-  </si>
-  <si>
-    <t>使攻击附加{0}，并对妖魔增伤{1.2}%。</t>
-  </si>
-  <si>
-    <t>对指定行的第一个目标造成{0}。</t>
-  </si>
-  <si>
-    <t>召唤一个生命值{0}，可以造成{1}的神兽为你作战，神兽可攻击{2}格目标。</t>
-  </si>
-  <si>
-    <t>对第一列所有目标造成{0}，并使其在当前回合无法攻击。</t>
-  </si>
-  <si>
-    <t>对任意一个目标造成{0}害并造成{1}回合的点燃效果，并且每回合会引燃临近的{2}个目标。</t>
-  </si>
-  <si>
-    <t>对指定行的第一个目标造成{0}，并对{1}个临近目标造成全额伤害。</t>
-  </si>
-  <si>
-    <t>随机对6个目标造成{0}，一定会选中被点燃的目标。</t>
-  </si>
-  <si>
-    <t>对指定2x2范围施展火墙，每回合对该格内的目标造成{0}，持续{1}回合。</t>
-  </si>
-  <si>
-    <t>对指定任意一个目标造成{0}。</t>
-  </si>
-  <si>
-    <t>对指定行所有目标造成{0}，法术命中-20%。</t>
-  </si>
-  <si>
-    <t>对指定2行或者2列的所有目标造成{0}。</t>
-  </si>
-  <si>
-    <t>对除中心点以外的所有目标造成{0}。</t>
-  </si>
-  <si>
-    <t>对指定行的第一个目标造成一次普通攻击并附加{0}。</t>
-  </si>
-  <si>
-    <t>bele</t>
-  </si>
-  <si>
-    <t>skwarr,battle,fdmg,tdmg,hdmg,pdmg</t>
-  </si>
-  <si>
-    <t>Ability_Warrior_WeaponMastery</t>
-  </si>
-  <si>
-    <t>元素剑术</t>
-  </si>
-  <si>
-    <t>使你的所有攻击能附带{0.2}%的元素伤害。当前增加{1}。</t>
+  </si>
+  <si>
+    <t>对最靠前的一列所有目标造成{0}。</t>
+  </si>
+  <si>
+    <t>降低{0}点物理减免，并增加{1}，持续{2}回合。</t>
+  </si>
+  <si>
+    <t>对指定行的第一个目标造成普通攻击{0.2}%的物理伤害。在下一回合中，该目标无法行动，同时，你优先行动。当前造成{1}。</t>
+  </si>
+  <si>
+    <t>hwoh</t>
+  </si>
+  <si>
+    <t>skmage,holy</t>
+  </si>
+  <si>
+    <t>Spell_Holy_Excorcism_02</t>
+  </si>
+  <si>
+    <t>圣言</t>
+  </si>
+  <si>
+    <t>有{0.2}%几率对不死或者妖魔目标造成其生命值25%的伤害。不受伤害加成类属性影响。</t>
+  </si>
+  <si>
+    <t>skwlok,psyco,summon,fire</t>
   </si>
 </sst>
 </file>
@@ -1224,17 +1253,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.54296875" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="50.81640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="8.7265625" style="3"/>
+    <col min="6" max="7" width="14.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="50.81640625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
@@ -1243,58 +1272,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>110</v>
+      <c r="E1" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>92</v>
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
@@ -1302,19 +1331,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>3</v>
@@ -1322,38 +1351,38 @@
       <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>93</v>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
@@ -1361,7 +1390,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -1369,58 +1398,58 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -1428,25 +1457,25 @@
         <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>116</v>
+      <c r="E5" s="3">
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1</v>
+      <c r="I5" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="J5" s="1">
         <v>3</v>
@@ -1469,28 +1498,28 @@
         <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="G6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="I6" s="3">
-        <v>7</v>
+      <c r="I6" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -1513,28 +1542,28 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="G7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I7" s="3">
-        <v>14</v>
+      <c r="I7" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="J7" s="1">
         <v>12</v>
@@ -1566,28 +1595,28 @@
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="G8" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="I8" s="3">
-        <v>21</v>
+      <c r="I8" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="J8" s="1">
         <v>27</v>
@@ -1613,28 +1642,28 @@
         <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="G9" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="I9" s="3">
-        <v>28</v>
+      <c r="I9" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="J9" s="1">
         <v>11</v>
@@ -1657,28 +1686,28 @@
         <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3">
+        <v>35</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="G10" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I10" s="3">
-        <v>35</v>
+      <c r="I10" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="J10" s="1">
         <v>24</v>
@@ -1704,25 +1733,25 @@
         <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>122</v>
+      <c r="E11" s="3">
+        <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1</v>
+      <c r="I11" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="J11" s="1">
         <v>25</v>
@@ -1751,25 +1780,25 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>123</v>
+      <c r="E12" s="3">
+        <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="I12" s="3">
-        <v>7</v>
+      <c r="I12" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
@@ -1792,28 +1821,28 @@
         <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="3">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="G13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I13" s="3">
-        <v>14</v>
+      <c r="I13" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -1836,28 +1865,28 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="3">
+        <v>21</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="G14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I14" s="3">
-        <v>21</v>
+      <c r="I14" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
@@ -1880,28 +1909,28 @@
         <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="3">
+        <v>28</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="G15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="I15" s="3">
-        <v>28</v>
       </c>
       <c r="J15" s="1">
         <v>25</v>
@@ -1921,28 +1950,28 @@
         <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="3">
+        <v>35</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="G16" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="I16" s="3">
-        <v>35</v>
+      <c r="I16" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="J16" s="1">
         <v>1</v>
@@ -1960,65 +1989,59 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>128</v>
+      <c r="E17" s="3">
+        <v>28</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1</v>
+        <v>223</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="J17" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K17" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="I18" s="3">
-        <v>7</v>
+        <v>125</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
@@ -2029,172 +2052,166 @@
     </row>
     <row r="19" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="G20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="I19" s="3">
-        <v>14</v>
-      </c>
-      <c r="J19" s="1">
-        <v>2</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="I20" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2</v>
+      </c>
+      <c r="K20" s="1">
         <v>8</v>
       </c>
-      <c r="L19" s="1">
-        <v>2</v>
-      </c>
-      <c r="M19" s="1">
+      <c r="L20" s="1">
+        <v>2</v>
+      </c>
+      <c r="M20" s="1">
         <v>4</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N20" s="1">
         <v>0.7</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O20" s="1">
         <v>5</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P20" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="s">
+    <row r="21" spans="1:19" ht="15" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>21</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I20" s="3">
-        <v>21</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>24</v>
+        <v>209</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I21" s="3">
-        <v>28</v>
+        <v>210</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="J21" s="1">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>76</v>
-      </c>
-      <c r="L21" s="1">
-        <v>10</v>
-      </c>
-      <c r="M21" s="1">
-        <v>31</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>59</v>
+      <c r="E22" s="3">
+        <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I22" s="3">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="J22" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K22" s="1">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="L22" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M22" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="N22" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
@@ -2202,28 +2219,28 @@
         <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>212</v>
+      <c r="E23" s="3">
+        <v>35</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>133</v>
+        <v>207</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I23" s="3">
-        <v>35</v>
+      <c r="I23" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="J23" s="1">
         <v>50</v>
@@ -2237,25 +2254,25 @@
         <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>134</v>
+      <c r="E24" s="3">
+        <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I24" s="3">
-        <v>1</v>
+      <c r="I24" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="J24" s="1">
         <v>2</v>
@@ -2272,128 +2289,140 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>135</v>
+        <v>2</v>
+      </c>
+      <c r="E25" s="3">
+        <v>7</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>28</v>
+        <v>213</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I25" s="3">
-        <v>7</v>
+        <v>214</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="J25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="1">
-        <v>0.5</v>
+        <v>5</v>
+      </c>
+      <c r="L25" s="1">
+        <v>2</v>
+      </c>
+      <c r="M25" s="1">
+        <v>5</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>14</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I26" s="3">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="J26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>4</v>
-      </c>
-      <c r="L26" s="1">
-        <v>1</v>
-      </c>
-      <c r="M26" s="1">
-        <v>2</v>
-      </c>
-      <c r="N26" s="1">
-        <v>4</v>
-      </c>
-      <c r="O26" s="1">
-        <v>8</v>
-      </c>
-      <c r="P26" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>4</v>
-      </c>
-      <c r="R26" s="1">
-        <v>1</v>
-      </c>
-      <c r="S26" s="1">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D27" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E27" s="3">
+        <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I27" s="3">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="J27" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K27" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M27" s="1">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="N27" s="1">
+        <v>4</v>
+      </c>
+      <c r="O27" s="1">
+        <v>8</v>
+      </c>
+      <c r="P27" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>4</v>
+      </c>
+      <c r="R27" s="1">
+        <v>1</v>
+      </c>
+      <c r="S27" s="1">
+        <v>0.35</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
@@ -2401,28 +2430,28 @@
         <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="3">
+        <v>28</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="G28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I28" s="3">
-        <v>28</v>
+      <c r="I28" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="J28" s="1">
         <v>120</v>
@@ -2436,28 +2465,28 @@
         <v>67</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="3">
+        <v>35</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="G29" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I29" s="3">
-        <v>35</v>
+      <c r="I29" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="J29" s="1">
         <v>1</v>
@@ -2477,37 +2506,34 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>140</v>
+      <c r="E30" s="3">
+        <v>21</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I30" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="J30" s="1">
         <v>5</v>
       </c>
       <c r="K30" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L30" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" s="1">
         <v>5</v>
@@ -2515,478 +2541,555 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D31" s="1">
-        <v>3</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>141</v>
+        <v>2</v>
+      </c>
+      <c r="E31" s="3">
+        <v>28</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I31" s="3">
-        <v>7</v>
+        <v>25</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="J31" s="1">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K31" s="1">
-        <v>0.5</v>
+        <v>101</v>
       </c>
       <c r="L31" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="M31" s="1">
-        <v>0.35</v>
+        <v>60</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>142</v>
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I32" s="3">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="J32" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K32" s="1">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="L32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>143</v>
+      <c r="E33" s="3">
+        <v>7</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="3">
-        <v>21</v>
+        <v>34</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="J33" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1">
-        <v>35</v>
+        <v>0.5</v>
       </c>
       <c r="L33" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M33" s="1">
-        <v>18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>145</v>
+      <c r="E34" s="3">
+        <v>14</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I34" s="3">
-        <v>28</v>
+        <v>35</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="J34" s="1">
         <v>1</v>
       </c>
       <c r="K34" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="L34" s="1">
-        <v>10</v>
-      </c>
-      <c r="M34" s="1">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>152</v>
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
+        <v>21</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="I35" s="3">
+        <v>36</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J35" s="1">
+        <v>20</v>
+      </c>
+      <c r="K35" s="1">
         <v>35</v>
       </c>
-      <c r="J35" s="1">
-        <v>3</v>
-      </c>
-      <c r="K35" s="1">
-        <v>300</v>
-      </c>
       <c r="L35" s="1">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="M35" s="1">
-        <v>2.2000000000000002</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E36" s="3">
+        <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I36" s="3">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="J36" s="1">
         <v>1</v>
       </c>
       <c r="K36" s="1">
-        <v>0.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>10</v>
+      </c>
+      <c r="M36" s="1">
+        <v>2.5</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D37" s="1">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E37" s="3">
+        <v>35</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>39</v>
+        <v>141</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I37" s="3">
-        <v>7</v>
+        <v>88</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="J37" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K37" s="1">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="L37" s="1">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M37" s="1">
-        <v>5</v>
-      </c>
-      <c r="N37" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="O37" s="1">
-        <v>4</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D38" s="1">
-        <v>3</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>148</v>
+        <v>1</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I38" s="3">
-        <v>14</v>
+        <v>38</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="J38" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>75</v>
-      </c>
-      <c r="L38" s="1">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1">
-        <v>2</v>
-      </c>
-      <c r="N38" s="1">
         <v>0.5</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="P38" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>0.25</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>149</v>
+      <c r="E39" s="3">
+        <v>7</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I39" s="3">
-        <v>21</v>
+        <v>39</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="J39" s="1">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>190</v>
+        <v>10</v>
       </c>
       <c r="L39" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="N39" s="1">
-        <v>2</v>
+        <v>0.33</v>
+      </c>
+      <c r="O39" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>150</v>
+        <v>3</v>
+      </c>
+      <c r="E40" s="3">
+        <v>14</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I40" s="3">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="J40" s="1">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="K40" s="1">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="L40" s="1">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="M40" s="1">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="N40" s="1">
-        <v>20</v>
+        <v>0.5</v>
+      </c>
+      <c r="O40" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="P40" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>0.25</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J41" s="1">
+        <v>54</v>
+      </c>
+      <c r="K41" s="1">
+        <v>190</v>
+      </c>
+      <c r="L41" s="1">
+        <v>27</v>
+      </c>
+      <c r="M41" s="1">
+        <v>95</v>
+      </c>
+      <c r="N41" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3">
+        <v>28</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J42" s="1">
+        <v>114</v>
+      </c>
+      <c r="K42" s="1">
+        <v>63</v>
+      </c>
+      <c r="L42" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M42" s="1">
+        <v>50</v>
+      </c>
+      <c r="N42" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D41" s="1">
+      <c r="B43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D43" s="1">
         <v>3</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E43" s="3">
+        <v>35</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="G43" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="I41" s="3">
-        <v>35</v>
-      </c>
-      <c r="J41" s="1">
+      <c r="I43" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J43" s="1">
         <v>350</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K43" s="1">
         <v>180</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L43" s="1">
         <v>44</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M43" s="1">
         <v>72</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N43" s="1">
         <v>21</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O43" s="1">
         <v>30</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P43" s="1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A11:A16">
+  <conditionalFormatting sqref="A11:A17">
     <cfRule type="duplicateValues" dxfId="4" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
+  <conditionalFormatting sqref="F13">
     <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
+  <conditionalFormatting sqref="F14">
     <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
+  <conditionalFormatting sqref="F15">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
+  <conditionalFormatting sqref="F16:F17">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98BFB81-E718-4AC6-B1EE-34779AE24AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BF252F-A2AB-4493-98F9-9746B6F789D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18610" yWindow="0" windowWidth="19880" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5510" yWindow="3710" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BF252F-A2AB-4493-98F9-9746B6F789D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D32A94-4EEE-4B83-9743-F57E6991F7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5510" yWindow="3710" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="231">
   <si>
     <t>id</t>
   </si>
@@ -842,6 +842,18 @@
   </si>
   <si>
     <t>skwlok,psyco,summon,fire</t>
+  </si>
+  <si>
+    <t>_hld</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Achievement_Dungeon_TheVioletHold</t>
+  </si>
+  <si>
+    <t>占位符</t>
   </si>
 </sst>
 </file>
@@ -1253,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
@@ -3070,6 +3082,29 @@
       </c>
       <c r="P43" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D32A94-4EEE-4B83-9743-F57E6991F7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4449B2E8-6187-42F3-A9FA-D073384F06F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="4080" windowWidth="32160" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -743,9 +743,6 @@
   </si>
   <si>
     <t>对任意指定目标造成{0}，并使其在接下来的{1}回合中无法施法。</t>
-  </si>
-  <si>
-    <t>对指定行的第一个目标造成一次普通攻击并附加普通攻击{0.2}%的火焰伤害。当前增加{1}。</t>
   </si>
   <si>
     <r>
@@ -855,16 +852,127 @@
   <si>
     <t>占位符</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对指定行的第一个目标造成一次普通攻击并附加物理攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0.2}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的火焰伤害。当前增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>{1}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每级学习的元素剑术可提供额外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{2.2}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加成，当前提升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{3.2}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -876,7 +984,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -897,6 +1005,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -936,7 +1051,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -1266,20 +1381,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S44"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" style="3"/>
-    <col min="6" max="7" width="14.7265625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="50.81640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7265625" style="1"/>
+    <col min="5" max="5" width="8.75" style="3"/>
+    <col min="6" max="7" width="14.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="50.875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1338,7 +1453,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1397,7 +1512,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1405,7 +1520,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1464,7 +1579,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
@@ -1505,7 +1620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -1549,7 +1664,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1602,7 +1717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
@@ -1649,7 +1764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1808,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
@@ -1740,7 +1855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -1787,7 +1902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
@@ -1828,7 +1943,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
@@ -1872,7 +1987,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1916,7 +2031,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
@@ -1957,7 +2072,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
@@ -2001,12 +2116,12 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -2015,13 +2130,13 @@
         <v>28</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="J17" s="1">
         <v>10</v>
@@ -2030,7 +2145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -2062,7 +2177,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -2097,7 +2212,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -2123,7 +2238,7 @@
         <v>23</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J20" s="1">
         <v>2</v>
@@ -2147,7 +2262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>207</v>
       </c>
@@ -2182,7 +2297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>59</v>
       </c>
@@ -2208,7 +2323,7 @@
         <v>24</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J22" s="1">
         <v>22</v>
@@ -2226,7 +2341,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -2251,8 +2366,8 @@
       <c r="H23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>216</v>
+      <c r="I23" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="J23" s="1">
         <v>50</v>
@@ -2260,8 +2375,11 @@
       <c r="K23" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L23" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
@@ -2299,7 +2417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>212</v>
       </c>
@@ -2346,7 +2464,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -2378,7 +2496,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>64</v>
       </c>
@@ -2404,7 +2522,7 @@
         <v>29</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J27" s="1">
         <v>2</v>
@@ -2437,7 +2555,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>66</v>
       </c>
@@ -2463,7 +2581,7 @@
         <v>31</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J28" s="1">
         <v>120</v>
@@ -2472,7 +2590,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>67</v>
       </c>
@@ -2516,7 +2634,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -2551,7 +2669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
@@ -2589,7 +2707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>68</v>
       </c>
@@ -2627,7 +2745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>69</v>
       </c>
@@ -2665,7 +2783,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>70</v>
       </c>
@@ -2697,7 +2815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>71</v>
       </c>
@@ -2738,7 +2856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>72</v>
       </c>
@@ -2779,7 +2897,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -2820,7 +2938,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -2852,7 +2970,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>75</v>
       </c>
@@ -2896,7 +3014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -2946,7 +3064,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,7 +3108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>77</v>
       </c>
@@ -3034,7 +3152,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>78</v>
       </c>
@@ -3042,7 +3160,7 @@
         <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -3084,27 +3202,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="I44" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4449B2E8-6187-42F3-A9FA-D073384F06F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F9605B-88EE-46B8-9F07-67FC9A7072A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="4080" windowWidth="32160" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="30825" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="234">
   <si>
     <t>id</t>
   </si>
@@ -963,6 +963,15 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>passive</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>被动</t>
+  </si>
 </sst>
 </file>
 
@@ -972,7 +981,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -984,7 +993,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1051,7 +1060,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -1380,21 +1389,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S44"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T44"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.75" style="3"/>
-    <col min="6" max="7" width="14.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="50.875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.75" style="1"/>
+    <col min="5" max="5" width="8.7109375" style="3"/>
+    <col min="6" max="8" width="14.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="50.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1417,43 +1426,46 @@
         <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1</v>
+        <v>231</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,13 +1488,13 @@
         <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>3</v>
+        <v>232</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>90</v>
@@ -1511,8 +1523,11 @@
       <c r="S2" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1520,7 +1535,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1543,43 +1558,46 @@
         <v>112</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
@@ -1598,29 +1616,32 @@
       <c r="G5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>3</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>7</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>2</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>4</v>
       </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -1642,29 +1663,32 @@
       <c r="G6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
       <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
         <v>2</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>0.1</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>0.2</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1686,38 +1710,41 @@
       <c r="G7" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>12</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>29</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>8</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>17</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>1.2</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>2</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <v>0.1</v>
       </c>
-      <c r="Q7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
@@ -1739,32 +1766,35 @@
       <c r="G8" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>27</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>93</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>18</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>36</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>1.25</v>
       </c>
-      <c r="O8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1786,29 +1816,32 @@
       <c r="G9" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>11</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>25</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>5</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>13</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
@@ -1830,32 +1863,35 @@
       <c r="G10" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>24</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>57</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>12</v>
       </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1">
         <v>32</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -1874,35 +1910,38 @@
       <c r="G11" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>25</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>5</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>75</v>
       </c>
-      <c r="M11" s="1">
-        <v>1</v>
-      </c>
       <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
         <v>0.25</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>8</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
@@ -1921,29 +1960,32 @@
       <c r="G12" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
       <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
         <v>22</v>
       </c>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
       <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
         <v>12</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>1.2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
@@ -1965,29 +2007,32 @@
       <c r="G13" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
       <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
         <v>35</v>
       </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
       <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
         <v>19</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -2009,29 +2054,32 @@
       <c r="G14" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
       <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
         <v>105</v>
       </c>
-      <c r="L14" s="1">
-        <v>1</v>
-      </c>
       <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
         <v>37</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
@@ -2053,26 +2101,29 @@
       <c r="G15" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>25</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>5</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <v>2</v>
       </c>
-      <c r="M15" s="1">
+      <c r="N15" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
@@ -2094,29 +2145,32 @@
       <c r="G16" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
       <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
         <v>72</v>
       </c>
-      <c r="L16" s="1">
-        <v>1</v>
-      </c>
       <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
         <v>45</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>220</v>
       </c>
@@ -2132,20 +2186,23 @@
       <c r="G17" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>10</v>
       </c>
-      <c r="K17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -2164,20 +2221,23 @@
       <c r="G18" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="J18" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
       <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -2199,20 +2259,23 @@
       <c r="G19" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="J19" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
       <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -2234,35 +2297,38 @@
       <c r="G20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="J20" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>2</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>8</v>
       </c>
-      <c r="L20" s="1">
+      <c r="M20" s="1">
         <v>2</v>
       </c>
-      <c r="M20" s="1">
+      <c r="N20" s="1">
         <v>4</v>
       </c>
-      <c r="N20" s="1">
+      <c r="O20" s="1">
         <v>0.7</v>
-      </c>
-      <c r="O20" s="1">
-        <v>5</v>
       </c>
       <c r="P20" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>207</v>
       </c>
@@ -2284,20 +2350,23 @@
       <c r="G21" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="J21" s="1">
-        <v>5</v>
       </c>
       <c r="K21" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="L21" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,29 +2388,32 @@
       <c r="G22" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>22</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>76</v>
       </c>
-      <c r="L22" s="1">
+      <c r="M22" s="1">
         <v>10</v>
       </c>
-      <c r="M22" s="1">
+      <c r="N22" s="1">
         <v>31</v>
       </c>
-      <c r="N22" s="1">
+      <c r="O22" s="1">
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -2363,23 +2435,26 @@
       <c r="G23" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>50</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>7</v>
       </c>
-      <c r="L23" s="1">
+      <c r="M23" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
@@ -2398,26 +2473,29 @@
       <c r="G24" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>2</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>4</v>
       </c>
-      <c r="L24" s="1">
-        <v>1</v>
-      </c>
       <c r="M24" s="1">
+        <v>1</v>
+      </c>
+      <c r="N24" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>212</v>
       </c>
@@ -2436,35 +2514,38 @@
       <c r="G25" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>2</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="L25" s="1">
+      <c r="M25" s="1">
         <v>2</v>
       </c>
-      <c r="M25" s="1">
+      <c r="N25" s="1">
         <v>5</v>
       </c>
-      <c r="N25" s="1">
+      <c r="O25" s="1">
         <v>0.9</v>
       </c>
-      <c r="O25" s="1">
-        <v>1</v>
-      </c>
       <c r="P25" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -2483,20 +2564,23 @@
       <c r="G26" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
       <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>64</v>
       </c>
@@ -2518,44 +2602,47 @@
       <c r="G27" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>2</v>
       </c>
-      <c r="K27" s="1">
+      <c r="L27" s="1">
         <v>4</v>
       </c>
-      <c r="L27" s="1">
-        <v>1</v>
-      </c>
       <c r="M27" s="1">
+        <v>1</v>
+      </c>
+      <c r="N27" s="1">
         <v>2</v>
       </c>
-      <c r="N27" s="1">
+      <c r="O27" s="1">
         <v>4</v>
       </c>
-      <c r="O27" s="1">
+      <c r="P27" s="1">
         <v>8</v>
       </c>
-      <c r="P27" s="1">
+      <c r="Q27" s="1">
         <v>2</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="R27" s="1">
         <v>4</v>
       </c>
-      <c r="R27" s="1">
-        <v>1</v>
-      </c>
       <c r="S27" s="1">
+        <v>1</v>
+      </c>
+      <c r="T27" s="1">
         <v>0.35</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>66</v>
       </c>
@@ -2577,20 +2664,23 @@
       <c r="G28" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>120</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>67</v>
       </c>
@@ -2612,29 +2702,32 @@
       <c r="G29" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
       <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
         <v>135</v>
       </c>
-      <c r="L29" s="1">
-        <v>1</v>
-      </c>
       <c r="M29" s="1">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1">
         <v>71</v>
       </c>
-      <c r="N29" s="1">
+      <c r="O29" s="1">
         <v>1.3</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -2650,26 +2743,29 @@
       <c r="G30" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J30" s="1">
+      <c r="K30" s="1">
         <v>5</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>9</v>
       </c>
-      <c r="L30" s="1">
+      <c r="M30" s="1">
         <v>3</v>
       </c>
-      <c r="M30" s="1">
+      <c r="N30" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
@@ -2685,29 +2781,32 @@
       <c r="G31" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J31" s="1">
+      <c r="K31" s="1">
         <v>32</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>101</v>
       </c>
-      <c r="L31" s="1">
+      <c r="M31" s="1">
         <v>18</v>
       </c>
-      <c r="M31" s="1">
+      <c r="N31" s="1">
         <v>60</v>
       </c>
-      <c r="N31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>68</v>
       </c>
@@ -2726,26 +2825,29 @@
       <c r="G32" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="J32" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J32" s="1">
+      <c r="K32" s="1">
         <v>5</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>10</v>
       </c>
-      <c r="L32" s="1">
+      <c r="M32" s="1">
         <v>2</v>
       </c>
-      <c r="M32" s="1">
+      <c r="N32" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>69</v>
       </c>
@@ -2764,26 +2866,29 @@
       <c r="G33" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="J33" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
       <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
         <v>0.5</v>
       </c>
-      <c r="L33" s="1">
+      <c r="M33" s="1">
         <v>3</v>
       </c>
-      <c r="M33" s="1">
+      <c r="N33" s="1">
         <v>0.35</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>70</v>
       </c>
@@ -2802,20 +2907,23 @@
       <c r="G34" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="J34" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>71</v>
       </c>
@@ -2837,26 +2945,29 @@
       <c r="G35" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="J35" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J35" s="1">
+      <c r="K35" s="1">
         <v>20</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>35</v>
       </c>
-      <c r="L35" s="1">
+      <c r="M35" s="1">
         <v>11</v>
       </c>
-      <c r="M35" s="1">
+      <c r="N35" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>72</v>
       </c>
@@ -2878,26 +2989,29 @@
       <c r="G36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="1">
-        <v>1</v>
-      </c>
       <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
         <v>0.1</v>
       </c>
-      <c r="L36" s="1">
+      <c r="M36" s="1">
         <v>10</v>
       </c>
-      <c r="M36" s="1">
+      <c r="N36" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -2919,26 +3033,29 @@
       <c r="G37" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="J37" s="1">
+      <c r="K37" s="1">
         <v>3</v>
       </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
         <v>300</v>
       </c>
-      <c r="L37" s="1">
+      <c r="M37" s="1">
         <v>155</v>
       </c>
-      <c r="M37" s="1">
+      <c r="N37" s="1">
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -2957,20 +3074,23 @@
       <c r="G38" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
       <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>75</v>
       </c>
@@ -2989,32 +3109,35 @@
       <c r="G39" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="J39" s="1">
-        <v>0</v>
-      </c>
       <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
         <v>10</v>
       </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
       <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
         <v>5</v>
       </c>
-      <c r="N39" s="1">
+      <c r="O39" s="1">
         <v>0.33</v>
       </c>
-      <c r="O39" s="1">
+      <c r="P39" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -3033,38 +3156,41 @@
       <c r="G40" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="J40" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="J40" s="1">
+      <c r="K40" s="1">
         <v>100</v>
       </c>
-      <c r="K40" s="1">
+      <c r="L40" s="1">
         <v>75</v>
       </c>
-      <c r="L40" s="1">
-        <v>1</v>
-      </c>
       <c r="M40" s="1">
+        <v>1</v>
+      </c>
+      <c r="N40" s="1">
         <v>2</v>
       </c>
-      <c r="N40" s="1">
+      <c r="O40" s="1">
         <v>0.5</v>
       </c>
-      <c r="O40" s="1">
+      <c r="P40" s="1">
         <v>0.9</v>
       </c>
-      <c r="P40" s="1">
-        <v>1</v>
-      </c>
       <c r="Q40" s="1">
+        <v>1</v>
+      </c>
+      <c r="R40" s="1">
         <v>0.25</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>76</v>
       </c>
@@ -3086,29 +3212,32 @@
       <c r="G41" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J41" s="1">
+      <c r="K41" s="1">
         <v>54</v>
       </c>
-      <c r="K41" s="1">
+      <c r="L41" s="1">
         <v>190</v>
       </c>
-      <c r="L41" s="1">
+      <c r="M41" s="1">
         <v>27</v>
       </c>
-      <c r="M41" s="1">
+      <c r="N41" s="1">
         <v>95</v>
       </c>
-      <c r="N41" s="1">
+      <c r="O41" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>77</v>
       </c>
@@ -3130,29 +3259,32 @@
       <c r="G42" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="J42" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J42" s="1">
+      <c r="K42" s="1">
         <v>114</v>
       </c>
-      <c r="K42" s="1">
+      <c r="L42" s="1">
         <v>63</v>
       </c>
-      <c r="L42" s="1">
+      <c r="M42" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M42" s="1">
+      <c r="N42" s="1">
         <v>50</v>
       </c>
-      <c r="N42" s="1">
+      <c r="O42" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>78</v>
       </c>
@@ -3174,35 +3306,38 @@
       <c r="G43" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="J43" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J43" s="1">
+      <c r="K43" s="1">
         <v>350</v>
       </c>
-      <c r="K43" s="1">
+      <c r="L43" s="1">
         <v>180</v>
       </c>
-      <c r="L43" s="1">
+      <c r="M43" s="1">
         <v>44</v>
       </c>
-      <c r="M43" s="1">
+      <c r="N43" s="1">
         <v>72</v>
       </c>
-      <c r="N43" s="1">
+      <c r="O43" s="1">
         <v>21</v>
       </c>
-      <c r="O43" s="1">
+      <c r="P43" s="1">
         <v>30</v>
       </c>
-      <c r="P43" s="1">
+      <c r="Q43" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>226</v>
       </c>
@@ -3218,10 +3353,13 @@
       <c r="G44" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="J44" s="1" t="s">
         <v>229</v>
       </c>
     </row>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F9605B-88EE-46B8-9F07-67FC9A7072A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379C8C22-5974-47D4-BC1B-058957BF2FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="30825" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="30825" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -830,9 +830,6 @@
   </si>
   <si>
     <t>Spell_Holy_Excorcism_02</t>
-  </si>
-  <si>
-    <t>圣言</t>
   </si>
   <si>
     <t>有{0.2}%几率对不死或者妖魔目标造成其生命值25%的伤害。不受伤害加成类属性影响。</t>
@@ -971,6 +968,9 @@
   </si>
   <si>
     <t>被动</t>
+  </si>
+  <si>
+    <t>圣言术</t>
   </si>
 </sst>
 </file>
@@ -1426,7 +1426,7 @@
         <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>3</v>
@@ -1558,7 +1558,7 @@
         <v>112</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>6</v>
@@ -2190,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="K17" s="1">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>26</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K23" s="1">
         <v>50</v>
@@ -3292,7 +3292,7 @@
         <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -3339,28 +3339,28 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="H44" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="J44" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Skill.xlsx
+++ b/configs/Skill.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379C8C22-5974-47D4-BC1B-058957BF2FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D934CC-8AE6-4964-B98C-23DB9ACD24D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="30825" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7880" yWindow="3340" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -836,18 +836,6 @@
   </si>
   <si>
     <t>skwlok,psyco,summon,fire</t>
-  </si>
-  <si>
-    <t>_hld</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>Achievement_Dungeon_TheVioletHold</t>
-  </si>
-  <si>
-    <t>占位符</t>
   </si>
   <si>
     <r>
@@ -971,6 +959,18 @@
   </si>
   <si>
     <t>圣言术</t>
+  </si>
+  <si>
+    <t>atak</t>
+  </si>
+  <si>
+    <t>Ability_SteelMelee</t>
+  </si>
+  <si>
+    <t>普通攻击</t>
+  </si>
+  <si>
+    <t>xdmg,other</t>
   </si>
 </sst>
 </file>
@@ -1390,20 +1390,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T44"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="3"/>
-    <col min="6" max="8" width="14.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="50.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="5" width="8.7265625" style="3"/>
+    <col min="6" max="8" width="14.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="50.81640625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -1465,7 +1465,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>112</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>6</v>
@@ -1597,53 +1597,38 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>230</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="H5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>9</v>
+        <v>232</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>196</v>
       </c>
       <c r="K5" s="1">
-        <v>3</v>
-      </c>
-      <c r="L5" s="1">
-        <v>7</v>
-      </c>
-      <c r="M5" s="1">
-        <v>2</v>
-      </c>
-      <c r="N5" s="1">
-        <v>4</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>98</v>
@@ -1655,42 +1640,39 @@
         <v>1</v>
       </c>
       <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K6" s="1">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
         <v>7</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>2</v>
       </c>
-      <c r="M6" s="1">
-        <v>0.1</v>
-      </c>
       <c r="N6" s="1">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="O6" s="1">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>98</v>
@@ -1699,54 +1681,45 @@
         <v>170</v>
       </c>
       <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="3">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="K7" s="1">
-        <v>12</v>
-      </c>
-      <c r="L7" s="1">
-        <v>29</v>
-      </c>
       <c r="M7" s="1">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="N7" s="1">
-        <v>17</v>
+        <v>0.2</v>
       </c>
       <c r="O7" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="P7" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="R7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>98</v>
@@ -1755,48 +1728,54 @@
         <v>170</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>45</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="K8" s="1">
         <v>12</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K8" s="1">
-        <v>27</v>
-      </c>
       <c r="L8" s="1">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="M8" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N8" s="1">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="O8" s="1">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="R8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>98</v>
@@ -1808,42 +1787,45 @@
         <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K9" s="1">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L9" s="1">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="M9" s="1">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N9" s="1">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="O9" s="1">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1.25</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>98</v>
@@ -1852,142 +1834,145 @@
         <v>170</v>
       </c>
       <c r="D10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K10" s="1">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L10" s="1">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="M10" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N10" s="1">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="O10" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="P10" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3">
+        <v>35</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K11" s="1">
+        <v>24</v>
+      </c>
+      <c r="L11" s="1">
+        <v>57</v>
+      </c>
+      <c r="M11" s="1">
+        <v>12</v>
+      </c>
+      <c r="N11" s="1">
+        <v>32</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="P11" s="1">
         <v>3</v>
       </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K11" s="1">
-        <v>25</v>
-      </c>
-      <c r="L11" s="1">
-        <v>5</v>
-      </c>
-      <c r="M11" s="1">
-        <v>75</v>
-      </c>
-      <c r="N11" s="1">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="P11" s="1">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="K12" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L12" s="1">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="M12" s="1">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="N12" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O12" s="1">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.25</v>
+      </c>
+      <c r="P12" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>98</v>
@@ -1999,42 +1984,39 @@
         <v>1</v>
       </c>
       <c r="E13" s="3">
-        <v>14</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H13" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M13" s="1">
         <v>1</v>
       </c>
       <c r="N13" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="O13" s="1">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>98</v>
@@ -2046,200 +2028,212 @@
         <v>1</v>
       </c>
       <c r="E14" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="M14" s="1">
         <v>1</v>
       </c>
       <c r="N14" s="1">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="O14" s="1">
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H15" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="K15" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="M15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="1">
+        <v>25</v>
+      </c>
+      <c r="L16" s="1">
+        <v>5</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>35</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="H17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
         <v>72</v>
       </c>
-      <c r="M16" s="1">
-        <v>1</v>
-      </c>
-      <c r="N16" s="1">
+      <c r="M17" s="1">
+        <v>1</v>
+      </c>
+      <c r="N17" s="1">
         <v>45</v>
       </c>
-      <c r="O16" s="1">
+      <c r="O17" s="1">
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
         <v>28</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H17" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J17" s="1" t="s">
+      <c r="H18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K18" s="1">
         <v>10</v>
       </c>
-      <c r="L17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>99</v>
@@ -2248,25 +2242,22 @@
         <v>174</v>
       </c>
       <c r="D19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3">
-        <v>7</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H19" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
@@ -2275,376 +2266,352 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
       </c>
       <c r="E20" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H20" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="K20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="1">
-        <v>8</v>
-      </c>
-      <c r="M20" s="1">
-        <v>2</v>
-      </c>
-      <c r="N20" s="1">
-        <v>4</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="P20" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="H21" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K21" s="1">
+        <v>2</v>
+      </c>
+      <c r="L21" s="1">
+        <v>8</v>
+      </c>
+      <c r="M21" s="1">
+        <v>2</v>
+      </c>
+      <c r="N21" s="1">
+        <v>4</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="P21" s="1">
         <v>5</v>
       </c>
-      <c r="L21" s="1">
+      <c r="Q21" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="15" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>207</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="D22" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="H22" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="K22" s="1">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L22" s="1">
-        <v>76</v>
-      </c>
-      <c r="M22" s="1">
-        <v>10</v>
-      </c>
-      <c r="N22" s="1">
-        <v>31</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>229</v>
+        <v>24</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="K23" s="1">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="L23" s="1">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="M23" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="N23" s="1">
+        <v>31</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="3">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H24" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>82</v>
+        <v>26</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="K24" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="L24" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M24" s="1">
-        <v>1</v>
-      </c>
-      <c r="N24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>212</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="H25" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>214</v>
+        <v>27</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="K25" s="1">
         <v>2</v>
       </c>
       <c r="L25" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M25" s="1">
+        <v>1</v>
+      </c>
+      <c r="N25" s="1">
         <v>2</v>
       </c>
-      <c r="N25" s="1">
-        <v>5</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="P25" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="H26" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="K26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="M26" s="1">
+        <v>2</v>
+      </c>
+      <c r="N26" s="1">
+        <v>5</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3">
-        <v>21</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H27" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="K27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="1">
-        <v>4</v>
-      </c>
-      <c r="M27" s="1">
-        <v>1</v>
-      </c>
-      <c r="N27" s="1">
-        <v>2</v>
-      </c>
-      <c r="O27" s="1">
-        <v>4</v>
-      </c>
-      <c r="P27" s="1">
-        <v>8</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>2</v>
-      </c>
-      <c r="R27" s="1">
-        <v>4</v>
-      </c>
-      <c r="S27" s="1">
-        <v>1</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>99</v>
@@ -2656,728 +2623,764 @@
         <v>2</v>
       </c>
       <c r="E28" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>64</v>
+        <v>212</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K28" s="1">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="L28" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M28" s="1">
+        <v>1</v>
+      </c>
+      <c r="N28" s="1">
+        <v>2</v>
+      </c>
+      <c r="O28" s="1">
+        <v>4</v>
+      </c>
+      <c r="P28" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>2</v>
+      </c>
+      <c r="R28" s="1">
+        <v>4</v>
+      </c>
+      <c r="S28" s="1">
+        <v>1</v>
+      </c>
+      <c r="T28" s="1">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
       <c r="E29" s="3">
+        <v>28</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K29" s="1">
+        <v>120</v>
+      </c>
+      <c r="L29" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="3">
         <v>35</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H29" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1" t="s">
+      <c r="H30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1">
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
         <v>135</v>
       </c>
-      <c r="M29" s="1">
-        <v>1</v>
-      </c>
-      <c r="N29" s="1">
+      <c r="M30" s="1">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1">
         <v>71</v>
       </c>
-      <c r="O29" s="1">
+      <c r="O30" s="1">
         <v>1.3</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
         <v>21</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H30" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I30" s="1" t="s">
+      <c r="H31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K31" s="1">
         <v>5</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L31" s="1">
         <v>9</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M31" s="1">
         <v>3</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N31" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>2</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E32" s="3">
         <v>28</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G32" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H31" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1" t="s">
+      <c r="H32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J32" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K32" s="1">
         <v>32</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L32" s="1">
         <v>101</v>
       </c>
-      <c r="M31" s="1">
+      <c r="M32" s="1">
         <v>18</v>
       </c>
-      <c r="N31" s="1">
+      <c r="N32" s="1">
         <v>60</v>
       </c>
-      <c r="O31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="O32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H32" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K32" s="1">
-        <v>5</v>
-      </c>
-      <c r="L32" s="1">
-        <v>10</v>
-      </c>
-      <c r="M32" s="1">
-        <v>2</v>
-      </c>
-      <c r="N32" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D33" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K33" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L33" s="1">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="M33" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" s="1">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D34" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="1">
+        <v>3</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D35" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="3">
-        <v>21</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K35" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L35" s="1">
-        <v>35</v>
-      </c>
-      <c r="M35" s="1">
-        <v>11</v>
-      </c>
-      <c r="N35" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D36" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K36" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L36" s="1">
-        <v>0.1</v>
+        <v>35</v>
       </c>
       <c r="M36" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N36" s="1">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="K37" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L37" s="1">
-        <v>300</v>
+        <v>0.1</v>
       </c>
       <c r="M37" s="1">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="N37" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="3">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H38" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K38" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L38" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="M38" s="1">
+        <v>155</v>
+      </c>
+      <c r="N38" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H39" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="1">
-        <v>10</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1">
-        <v>5</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="P39" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D40" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H40" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="M40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O40" s="1">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="P40" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>1</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D41" s="1">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3">
+        <v>14</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1">
+        <v>75</v>
+      </c>
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+      <c r="N41" s="1">
         <v>2</v>
       </c>
-      <c r="E41" s="3">
-        <v>21</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H41" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K41" s="1">
-        <v>54</v>
-      </c>
-      <c r="L41" s="1">
-        <v>190</v>
-      </c>
-      <c r="M41" s="1">
-        <v>27</v>
-      </c>
-      <c r="N41" s="1">
-        <v>95</v>
-      </c>
       <c r="O41" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>1</v>
+      </c>
+      <c r="R41" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K42" s="1">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="L42" s="1">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="M42" s="1">
-        <v>2.2000000000000002</v>
+        <v>27</v>
       </c>
       <c r="N42" s="1">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="O42" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3">
+        <v>28</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K43" s="1">
+        <v>114</v>
+      </c>
+      <c r="L43" s="1">
+        <v>63</v>
+      </c>
+      <c r="M43" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N43" s="1">
+        <v>50</v>
+      </c>
+      <c r="O43" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D44" s="1">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E44" s="3">
         <v>35</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H43" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" s="1" t="s">
+      <c r="H44" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J44" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K44" s="1">
         <v>350</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L44" s="1">
         <v>180</v>
       </c>
-      <c r="M43" s="1">
+      <c r="M44" s="1">
         <v>44</v>
       </c>
-      <c r="N43" s="1">
+      <c r="N44" s="1">
         <v>72</v>
       </c>
-      <c r="O43" s="1">
+      <c r="O44" s="1">
         <v>21</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P44" s="1">
         <v>30</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="Q44" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H44" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A11:A17">
+  <conditionalFormatting sqref="A12:A18">
     <cfRule type="duplicateValues" dxfId="4" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
+  <conditionalFormatting sqref="F14">
     <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
+  <conditionalFormatting sqref="F15">
     <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F16">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F17">
+  <conditionalFormatting sqref="F17:F18">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
